--- a/python/other/Protein Costs.xlsx
+++ b/python/other/Protein Costs.xlsx
@@ -9,7 +9,7 @@
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Pivot!$A$1:$B$65</definedName>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Data!$A$1:$V$64</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Data!$A$1:$V$67</definedName>
   </definedNames>
   <calcPr/>
   <pivotCaches>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="165">
   <si>
     <t>Food</t>
   </si>
@@ -48,19 +48,19 @@
     <t>Boneless Skinless Chicken Breast</t>
   </si>
   <si>
+    <t>Vital Wheat Gluten</t>
+  </si>
+  <si>
+    <t>Canned Salmon</t>
+  </si>
+  <si>
+    <t>Egg Whites</t>
+  </si>
+  <si>
     <t>Pork Loin</t>
   </si>
   <si>
-    <t>Vital Wheat Gluten</t>
-  </si>
-  <si>
-    <t>Canned Salmon</t>
-  </si>
-  <si>
-    <t>Egg Whites</t>
-  </si>
-  <si>
-    <t>Large Eggs</t>
+    <t>Whole Eggs</t>
   </si>
   <si>
     <t>Plain Nonfat Greek Yogurt</t>
@@ -120,6 +120,9 @@
     <t>Powdered Peanut Butter</t>
   </si>
   <si>
+    <t>85% Lean Ground Turkey</t>
+  </si>
+  <si>
     <t>93% Lean Ground Beef</t>
   </si>
   <si>
@@ -138,27 +141,36 @@
     <t>Canned Black Beans</t>
   </si>
   <si>
+    <t>Canned Sardines</t>
+  </si>
+  <si>
     <t>Frozen Cooked Shrimp (Peeled, Deveined, Tail-off)</t>
   </si>
   <si>
+    <t>85% Lean Ground Beef</t>
+  </si>
+  <si>
     <t>Processed Peanut Butter</t>
   </si>
   <si>
     <t>Canned Light Red Kidney Beans</t>
   </si>
   <si>
-    <t>Canned Sardines</t>
-  </si>
-  <si>
     <t>Canned Pinto Beans</t>
   </si>
   <si>
+    <t>Fresh Clams</t>
+  </si>
+  <si>
     <t>Canned Dark Red Kidney Beans</t>
   </si>
   <si>
     <t>Canned Lentils</t>
   </si>
   <si>
+    <t>80% Lean Ground Beef</t>
+  </si>
+  <si>
     <t>Canned Chickpeas</t>
   </si>
   <si>
@@ -195,9 +207,6 @@
     <t>Tri-Color Quinoa</t>
   </si>
   <si>
-    <t>Fresh Clams</t>
-  </si>
-  <si>
     <t>Russet Potatoes</t>
   </si>
   <si>
@@ -291,7 +300,16 @@
     <t>https://www.walmart.com/ip/Shady-Brook-Farms-93-Lean-7-Fat-Ground-Turkey-Tray-Fresh-3-lbs/161873862?athbdg=L1300&amp;from=/search</t>
   </si>
   <si>
+    <t>https://www.nutritionvalue.org/Turkey%2C_raw%2C_15%25_fat%2C_85%25_lean%2C_ground_nutritional_value.html?size=112+g&amp;utm_source=share-by-url</t>
+  </si>
+  <si>
     <t>https://www.walmart.com/ip/All-Natural-93-Lean-7-Fat-Lean-Ground-Beef-4-5-lb-Tray/519269784?from=/search</t>
+  </si>
+  <si>
+    <t>https://www.nutritionvalue.org/Beef%2C_raw%2C_85%25_lean_meat_%252F_15%25_fat%2C_ground_nutritional_value.html?size=112+g&amp;utm_source=share-by-url</t>
+  </si>
+  <si>
+    <t>https://www.nutritionvalue.org/Beef%2C_raw%2C_80%25_lean_meat_%252F_20%25_fat%2C_ground_nutritional_value.html?size=112+g&amp;utm_source=share-by-url</t>
   </si>
   <si>
     <t>https://www.walmart.com/ip/Beef-Sirloin-Tip-Steak-Thin-0-85-1-61-lb-Tray/21553581?from=/search</t>
@@ -656,9 +674,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -686,7 +704,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:V64" sheet="Data"/>
+    <worksheetSource ref="A1:V67" sheet="Data"/>
   </cacheSource>
   <cacheFields>
     <cacheField name="Food" numFmtId="0">
@@ -695,7 +713,10 @@
         <s v="Boneless Skinless Chicken Thighs"/>
         <s v="Bone In Skin On Chicken Thighs"/>
         <s v="93% Lean Ground Turkey"/>
+        <s v="85% Lean Ground Turkey"/>
         <s v="93% Lean Ground Beef"/>
+        <s v="85% Lean Ground Beef"/>
+        <s v="80% Lean Ground Beef"/>
         <s v="Beef Sirloin Tip Steak"/>
         <s v="Pork Loin"/>
         <s v="Canned Tuna"/>
@@ -709,7 +730,7 @@
         <s v="Fresh Clams"/>
         <s v="Frozen Raw Shrimp (Peeled, Deveined, Tail-off)"/>
         <s v="Frozen Cooked Shrimp (Peeled, Deveined, Tail-off)"/>
-        <s v="Large Eggs"/>
+        <s v="Whole Eggs"/>
         <s v="Egg Whites"/>
         <s v="Processed Peanut Butter"/>
         <s v="Natural Peanut Butter"/>
@@ -775,8 +796,11 @@
         <n v="12.18"/>
         <n v="14.06"/>
         <n v="9.06"/>
-        <n v="11.98"/>
-        <n v="27.97"/>
+        <n v="4.99"/>
+        <n v="4.5"/>
+        <n v="6.99"/>
+        <n v="5.99"/>
+        <n v="5.49"/>
         <n v="9.93"/>
         <n v="11.0"/>
         <n v="3.28"/>
@@ -832,8 +856,8 @@
         <n v="2070.24"/>
         <n v="2156.5"/>
         <n v="2324.48"/>
-        <n v="1362.0"/>
-        <n v="2043.0"/>
+        <n v="590.2"/>
+        <n v="454.0"/>
         <n v="576.58"/>
         <n v="2133.8"/>
         <n v="566.0"/>
@@ -842,7 +866,6 @@
         <n v="340.5"/>
         <n v="408.6"/>
         <n v="908.0"/>
-        <n v="454.0"/>
         <n v="183.95000000000002"/>
         <n v="219.608"/>
         <n v="339.6"/>
@@ -866,6 +889,7 @@
         <n v="283.0"/>
         <n v="4540.0"/>
         <n v="2270.0"/>
+        <n v="1362.0"/>
         <n v="1816.0"/>
       </sharedItems>
     </cacheField>
@@ -874,8 +898,11 @@
         <n v="2.671052631578948"/>
         <n v="2.96"/>
         <n v="1.7695312500000002"/>
-        <n v="3.993333333333333"/>
-        <n v="6.2155555555555555"/>
+        <n v="3.838461538461538"/>
+        <n v="3.4615384615384612"/>
+        <n v="6.99"/>
+        <n v="5.99"/>
+        <n v="5.49"/>
         <n v="7.818897637795275"/>
         <n v="2.340425531914893"/>
         <n v="2.63095406360424"/>
@@ -937,7 +964,11 @@
         <n v="140.0"/>
         <n v="160.0"/>
         <n v="250.0"/>
+        <n v="168.0"/>
+        <n v="202.0"/>
         <n v="170.0"/>
+        <n v="241.0"/>
+        <n v="284.0"/>
         <n v="190.0"/>
         <n v="100.0"/>
         <n v="120.0"/>
@@ -963,7 +994,10 @@
         <n v="166.0"/>
         <n v="247.0"/>
         <n v="160.0"/>
+        <n v="202.0"/>
         <n v="164.0"/>
+        <n v="237.0"/>
+        <n v="274.0"/>
         <n v="155.0"/>
         <n v="182.0"/>
         <n v="100.0"/>
@@ -1045,18 +1079,18 @@
         <n v="18.48428571428571"/>
         <n v="19.254464285714285"/>
         <n v="20.754285714285714"/>
-        <n v="12.160714285714286"/>
-        <n v="18.241071428571427"/>
+        <n v="5.269642857142857"/>
+        <n v="4.053571428571429"/>
         <n v="5.148035714285714"/>
         <n v="19.051785714285717"/>
-        <n v="4.0"/>
+        <n v="5.008849557522124"/>
         <n v="4.910882352941177"/>
-        <n v="1.0"/>
+        <n v="1.5160714285714285"/>
         <n v="3.0401785714285716"/>
         <n v="3.615929203539823"/>
         <n v="8.107142857142858"/>
-        <n v="4.053571428571429"/>
         <n v="2.164117647058824"/>
+        <n v="2.6143809523809525"/>
         <n v="4.042857142857143"/>
         <n v="18.0"/>
         <n v="19.68695652173913"/>
@@ -1101,12 +1135,12 @@
         <n v="19.0"/>
         <n v="22.0"/>
         <n v="23.0"/>
+        <n v="21.0"/>
         <n v="20.0"/>
         <n v="12.0"/>
         <n v="27.0"/>
         <n v="17.0"/>
         <n v="5.0"/>
-        <n v="21.0"/>
         <n v="15.0"/>
         <n v="7.0"/>
         <n v="8.0"/>
@@ -1128,6 +1162,9 @@
         <n v="10.0"/>
         <n v="19.0"/>
         <n v="8.0"/>
+        <n v="14.0"/>
+        <n v="17.0"/>
+        <n v="22.0"/>
         <n v="7.0"/>
         <n v="0.0"/>
         <n v="5.0"/>
@@ -1185,8 +1222,11 @@
         <n v="0.7142857142857143"/>
         <n v="0.475"/>
         <n v="0.304"/>
-        <n v="0.55"/>
+        <n v="0.5238095238095238"/>
+        <n v="0.37623762376237624"/>
         <n v="0.5411764705882353"/>
+        <n v="0.34854771784232363"/>
+        <n v="0.2676056338028169"/>
         <n v="0.575"/>
         <n v="0.4842105263157895"/>
         <n v="1.0"/>
@@ -1238,8 +1278,11 @@
         <n v="0.2571428571428571"/>
         <n v="0.5625"/>
         <n v="0.684"/>
-        <n v="0.45"/>
+        <n v="0.42857142857142855"/>
+        <n v="0.6237623762376238"/>
         <n v="0.4235294117647059"/>
+        <n v="0.6348547717842323"/>
+        <n v="0.6971830985915493"/>
         <n v="0.39375"/>
         <n v="0.47368421052631576"/>
         <n v="0.0"/>
@@ -1310,19 +1353,22 @@
         <n v="0.026357523765360543"/>
         <n v="0.038432645490377934"/>
         <n v="0.02297559703222815"/>
-        <n v="0.044779068215191564"/>
-        <n v="0.06666751792972823"/>
+        <n v="0.04304242013493115"/>
+        <n v="0.04494462180527564"/>
+        <n v="0.07497414288450488"/>
+        <n v="0.07036710719530102"/>
+        <n v="0.07128217018316717"/>
         <n v="0.08386482813953944"/>
         <n v="0.02510320432622755"/>
-        <n v="0.032799999999999996"/>
+        <n v="0.02619363957597173"/>
         <n v="0.030544409175300952"/>
-        <n v="0.08166666666666667"/>
+        <n v="0.05386729485669415"/>
         <n v="0.0910034263338228"/>
         <n v="0.10460958947838854"/>
         <n v="0.06998376999768141"/>
         <n v="0.11551179061933142"/>
         <n v="0.20146779016036964"/>
-        <n v="0.4276190476190476"/>
+        <n v="0.1635641688827365"/>
         <n v="0.10640822320117474"/>
         <n v="0.11254416961130742"/>
         <n v="0.018492063492063494"/>
@@ -1371,9 +1417,8 @@
       </sharedItems>
     </cacheField>
     <cacheField name="PDCAAS" numFmtId="4">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1">
         <n v="1.0"/>
-        <m/>
         <n v="0.509"/>
         <n v="0.7949999999999999"/>
         <n v="0.648"/>
@@ -1410,7 +1455,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1">
         <n v="1.04"/>
         <n v="1.058"/>
-        <n v="1.17"/>
+        <n v="1.085"/>
         <n v="1.0"/>
         <n v="1.065"/>
         <n v="0.47150000000000003"/>
@@ -1433,19 +1478,22 @@
         <n v="28.183874535035685"/>
         <n v="12.853655888030886"/>
         <n v="13.760687026174706"/>
-        <n v="12.77382542332459"/>
-        <n v="8.588360923919085"/>
+        <n v="12.656395784766813"/>
+        <n v="8.705983341191262"/>
+        <n v="7.636828963344995"/>
+        <n v="5.240566227252891"/>
+        <n v="3.971915555262357"/>
         <n v="7.253934855596317"/>
-        <n v="22.567888482570062"/>
-        <n v="30.487804878048784"/>
+        <n v="20.928341028708136"/>
+        <n v="38.17720699330887"/>
         <n v="21.82614379084967"/>
-        <n v="4.521193092621664"/>
+        <n v="6.854451670778202"/>
         <n v="9.88973752151463"/>
         <n v="3.664418675617944"/>
         <n v="12.066289719350946"/>
         <n v="7.3585561737257725"/>
         <n v="2.481786292498651"/>
-        <n v="1.6369710467706011"/>
+        <n v="4.279665924276169"/>
         <n v="7.048327445352175"/>
         <n v="6.092845929580624"/>
         <n v="20.157296137339053"/>
@@ -1501,7 +1549,10 @@
         <s v="https://www.walmart.com/ip/Boneless-Skinless-Chicken-Thighs-Family-Pack-4-7-6-lb-Tray/124782654?athbdg=L1600&amp;from=/search"/>
         <s v="https://www.walmart.com/ip/Perdue-No-Antibiotics-Ever-Fresh-Chicken-Thighs-4-5-5-9-lb-Tray/51259012?from=/search"/>
         <s v="https://www.walmart.com/ip/Shady-Brook-Farms-93-Lean-7-Fat-Ground-Turkey-Tray-Fresh-3-lbs/161873862?athbdg=L1300&amp;from=/search"/>
+        <s v="https://www.nutritionvalue.org/Turkey%2C_raw%2C_15%25_fat%2C_85%25_lean%2C_ground_nutritional_value.html?size=112+g&amp;utm_source=share-by-url"/>
         <s v="https://www.walmart.com/ip/All-Natural-93-Lean-7-Fat-Lean-Ground-Beef-4-5-lb-Tray/519269784?from=/search"/>
+        <s v="https://www.nutritionvalue.org/Beef%2C_raw%2C_85%25_lean_meat_%252F_15%25_fat%2C_ground_nutritional_value.html?size=112+g&amp;utm_source=share-by-url"/>
+        <s v="https://www.nutritionvalue.org/Beef%2C_raw%2C_80%25_lean_meat_%252F_20%25_fat%2C_ground_nutritional_value.html?size=112+g&amp;utm_source=share-by-url"/>
         <s v="https://www.walmart.com/ip/Beef-Sirloin-Tip-Steak-Thin-0-85-1-61-lb-Tray/21553581?from=/search"/>
         <s v="https://www.walmart.com/ip/AVA-Brand-Center-Cut-Loin-Roast-Boneless-Fresh-Pork-4-0-5-5-lb-Fresh/106173246?from=/search"/>
         <s v="https://www.walmart.com/ip/Great-Value-Chunk-Light-Tuna-in-Water-5-oz-4-Pack/33867594?athbdg=L1200&amp;from=/search"/>
@@ -1568,7 +1619,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Pivot" cacheId="0" dataCaption="" rowGrandTotals="0" compact="0" compactData="0">
-  <location ref="A1:E64" firstHeaderRow="0" firstDataRow="2" firstDataCol="0"/>
+  <location ref="A1:E67" firstHeaderRow="0" firstDataRow="2" firstDataCol="0"/>
   <pivotFields>
     <pivotField name="Food" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
       <items>
@@ -1635,6 +1686,9 @@
         <item x="60"/>
         <item x="61"/>
         <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -1717,6 +1771,9 @@
         <item x="50"/>
         <item x="51"/>
         <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1824,6 +1881,9 @@
         <item x="56"/>
         <item x="57"/>
         <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1850,6 +1910,10 @@
         <item x="18"/>
         <item x="19"/>
         <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1904,6 +1968,9 @@
         <item x="46"/>
         <item x="47"/>
         <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2038,6 +2105,9 @@
         <item x="11"/>
         <item x="12"/>
         <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2134,6 +2204,9 @@
         <item x="46"/>
         <item x="47"/>
         <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2167,6 +2240,9 @@
         <item x="25"/>
         <item x="26"/>
         <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2274,6 +2350,9 @@
         <item x="58"/>
         <item x="59"/>
         <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2291,7 +2370,6 @@
         <item x="9"/>
         <item x="10"/>
         <item x="11"/>
-        <item x="12"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2403,6 +2481,9 @@
         <item x="60"/>
         <item x="61"/>
         <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2471,6 +2552,9 @@
         <item x="60"/>
         <item x="61"/>
         <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2762,6 +2846,9 @@
     <row r="62"/>
     <row r="63"/>
     <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
   </sheetData>
   <autoFilter ref="$A$1:$B$65">
     <sortState ref="A1:B65">
@@ -2812,58 +2899,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N1" s="10" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T1" s="11" t="s">
         <v>3</v>
@@ -2872,7 +2959,7 @@
         <v>1</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="W1" s="12"/>
       <c r="X1" s="12"/>
@@ -2894,7 +2981,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C2" s="14">
         <v>12.18</v>
@@ -2904,21 +2991,21 @@
         <v>2070.24</v>
       </c>
       <c r="E2" s="3">
-        <f t="shared" ref="E2:E64" si="1">C2/D2*454</f>
+        <f t="shared" ref="E2:E67" si="1">C2/D2*454</f>
         <v>2.671052632</v>
       </c>
       <c r="F2" s="16">
         <v>140.0</v>
       </c>
       <c r="G2" s="17">
-        <f t="shared" ref="G2:G64" si="2">(J2*4)+(K2*9)+((L2-M2)*4)</f>
+        <f t="shared" ref="G2:G67" si="2">(J2*4)+(K2*9)+((L2-M2)*4)</f>
         <v>136</v>
       </c>
       <c r="H2" s="16">
         <v>112.0</v>
       </c>
       <c r="I2" s="18">
-        <f t="shared" ref="I2:I8" si="3">D2/H2</f>
+        <f t="shared" ref="I2:I67" si="3">D2/H2</f>
         <v>18.48428571</v>
       </c>
       <c r="J2" s="16">
@@ -2934,19 +3021,19 @@
         <v>0.0</v>
       </c>
       <c r="N2" s="4">
-        <f t="shared" ref="N2:N64" si="4">(J2*4)/F2</f>
+        <f t="shared" ref="N2:N67" si="4">(J2*4)/F2</f>
         <v>0.7142857143</v>
       </c>
       <c r="O2" s="4">
-        <f t="shared" ref="O2:O64" si="5">(K2*9)/F2</f>
+        <f t="shared" ref="O2:O67" si="5">(K2*9)/F2</f>
         <v>0.2571428571</v>
       </c>
       <c r="P2" s="4">
-        <f t="shared" ref="P2:P64" si="6">(L2*4)/F2</f>
+        <f t="shared" ref="P2:P67" si="6">(L2*4)/F2</f>
         <v>0</v>
       </c>
       <c r="Q2" s="14">
-        <f t="shared" ref="Q2:Q64" si="7">C2/(J2*I2)</f>
+        <f t="shared" ref="Q2:Q67" si="7">C2/(J2*I2)</f>
         <v>0.02635752377</v>
       </c>
       <c r="R2" s="19">
@@ -2960,11 +3047,11 @@
         <v>1.04</v>
       </c>
       <c r="U2" s="19">
-        <f t="shared" ref="U2:U64" si="9">N2*T2/Q2</f>
+        <f t="shared" ref="U2:U67" si="9">(N2*T2)/Q2</f>
         <v>28.18387454</v>
       </c>
       <c r="V2" s="20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="W2" s="21"/>
       <c r="X2" s="21"/>
@@ -2986,7 +3073,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C3" s="14">
         <v>14.06</v>
@@ -3007,7 +3094,8 @@
         <v>166</v>
       </c>
       <c r="H3" s="16">
-        <v>112.0</v>
+        <f t="shared" ref="H3:H11" si="10">H2</f>
+        <v>112</v>
       </c>
       <c r="I3" s="18">
         <f t="shared" si="3"/>
@@ -3050,7 +3138,7 @@
         <v>1.08</v>
       </c>
       <c r="T3" s="19">
-        <f t="shared" ref="T3:T64" si="11">AVERAGE(R3,S3)</f>
+        <f t="shared" ref="T3:T67" si="12">AVERAGE(R3,S3)</f>
         <v>1.04</v>
       </c>
       <c r="U3" s="19">
@@ -3058,7 +3146,7 @@
         <v>12.85365589</v>
       </c>
       <c r="V3" s="23" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AJ3" s="24"/>
     </row>
@@ -3067,7 +3155,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C4" s="14">
         <v>9.06</v>
@@ -3088,7 +3176,8 @@
         <v>247</v>
       </c>
       <c r="H4" s="16">
-        <v>112.0</v>
+        <f t="shared" si="10"/>
+        <v>112</v>
       </c>
       <c r="I4" s="18">
         <f t="shared" si="3"/>
@@ -3123,15 +3212,15 @@
         <v>0.02297559703</v>
       </c>
       <c r="R4" s="19">
-        <f t="shared" ref="R4:S4" si="10">R2</f>
+        <f t="shared" ref="R4:S4" si="11">R2</f>
         <v>1</v>
       </c>
       <c r="S4" s="19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.08</v>
       </c>
       <c r="T4" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.04</v>
       </c>
       <c r="U4" s="19">
@@ -3139,7 +3228,7 @@
         <v>13.76068703</v>
       </c>
       <c r="V4" s="20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AJ4" s="24"/>
     </row>
@@ -3148,32 +3237,33 @@
         <v>25</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C5" s="14">
-        <v>11.98</v>
+        <v>4.99</v>
       </c>
       <c r="D5" s="15">
-        <f>3*454</f>
-        <v>1362</v>
+        <f>1.3*454</f>
+        <v>590.2</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="1"/>
-        <v>3.993333333</v>
+        <v>3.838461538</v>
       </c>
       <c r="F5" s="16">
-        <v>160.0</v>
+        <v>168.0</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="H5" s="16">
-        <v>112.0</v>
+        <f t="shared" si="10"/>
+        <v>112</v>
       </c>
       <c r="I5" s="18">
         <f t="shared" si="3"/>
-        <v>12.16071429</v>
+        <v>5.269642857</v>
       </c>
       <c r="J5" s="16">
         <v>22.0</v>
@@ -3189,11 +3279,11 @@
       </c>
       <c r="N5" s="4">
         <f t="shared" si="4"/>
-        <v>0.55</v>
+        <v>0.5238095238</v>
       </c>
       <c r="O5" s="4">
         <f t="shared" si="5"/>
-        <v>0.45</v>
+        <v>0.4285714286</v>
       </c>
       <c r="P5" s="4">
         <f t="shared" si="6"/>
@@ -3201,26 +3291,26 @@
       </c>
       <c r="Q5" s="14">
         <f t="shared" si="7"/>
-        <v>0.04477906822</v>
+        <v>0.04304242013</v>
       </c>
       <c r="R5" s="19">
-        <f t="shared" ref="R5:S5" si="12">R2</f>
+        <f t="shared" ref="R5:S5" si="13">R2</f>
         <v>1</v>
       </c>
       <c r="S5" s="19">
+        <f t="shared" si="13"/>
+        <v>1.08</v>
+      </c>
+      <c r="T5" s="19">
         <f t="shared" si="12"/>
-        <v>1.08</v>
-      </c>
-      <c r="T5" s="19">
-        <f t="shared" si="11"/>
         <v>1.04</v>
       </c>
       <c r="U5" s="19">
         <f t="shared" si="9"/>
-        <v>12.77382542</v>
+        <v>12.65639578</v>
       </c>
       <c r="V5" s="20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AJ5" s="24"/>
     </row>
@@ -3229,38 +3319,39 @@
         <v>33</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C6" s="14">
-        <v>27.97</v>
-      </c>
-      <c r="D6" s="25">
-        <f>4.5*454</f>
-        <v>2043</v>
+        <v>4.5</v>
+      </c>
+      <c r="D6" s="15">
+        <f>D5</f>
+        <v>590.2</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" si="1"/>
-        <v>6.215555556</v>
+        <v>3.461538462</v>
       </c>
       <c r="F6" s="16">
-        <v>170.0</v>
+        <v>202.0</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="H6" s="16">
-        <v>112.0</v>
+        <f t="shared" si="10"/>
+        <v>112</v>
       </c>
       <c r="I6" s="18">
         <f t="shared" si="3"/>
-        <v>18.24107143</v>
+        <v>5.269642857</v>
       </c>
       <c r="J6" s="16">
-        <v>23.0</v>
+        <v>19.0</v>
       </c>
       <c r="K6" s="16">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="L6" s="16">
         <v>0.0</v>
@@ -3270,11 +3361,11 @@
       </c>
       <c r="N6" s="4">
         <f t="shared" si="4"/>
-        <v>0.5411764706</v>
+        <v>0.3762376238</v>
       </c>
       <c r="O6" s="4">
         <f t="shared" si="5"/>
-        <v>0.4235294118</v>
+        <v>0.6237623762</v>
       </c>
       <c r="P6" s="4">
         <f t="shared" si="6"/>
@@ -3282,64 +3373,66 @@
       </c>
       <c r="Q6" s="14">
         <f t="shared" si="7"/>
-        <v>0.06666751793</v>
+        <v>0.04494462181</v>
       </c>
       <c r="R6" s="19">
-        <v>1.0</v>
+        <f t="shared" ref="R6:S6" si="14">R5</f>
+        <v>1</v>
       </c>
       <c r="S6" s="19">
-        <v>1.116</v>
+        <f t="shared" si="14"/>
+        <v>1.08</v>
       </c>
       <c r="T6" s="19">
-        <f t="shared" si="11"/>
-        <v>1.058</v>
+        <f t="shared" si="12"/>
+        <v>1.04</v>
       </c>
       <c r="U6" s="19">
         <f t="shared" si="9"/>
-        <v>8.588360924</v>
+        <v>8.705983341</v>
       </c>
       <c r="V6" s="20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AJ6" s="24"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C7" s="14">
-        <v>9.93</v>
+        <v>6.99</v>
       </c>
       <c r="D7" s="15">
-        <f>1.27*454</f>
-        <v>576.58</v>
+        <v>454.0</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="1"/>
-        <v>7.818897638</v>
+        <v>6.99</v>
       </c>
       <c r="F7" s="16">
-        <v>160.0</v>
+        <v>170.0</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="2"/>
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H7" s="16">
-        <v>112.0</v>
+        <f t="shared" si="10"/>
+        <v>112</v>
       </c>
       <c r="I7" s="18">
         <f t="shared" si="3"/>
-        <v>5.148035714</v>
+        <v>4.053571429</v>
       </c>
       <c r="J7" s="16">
         <v>23.0</v>
       </c>
       <c r="K7" s="16">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="L7" s="16">
         <v>0.0</v>
@@ -3349,11 +3442,11 @@
       </c>
       <c r="N7" s="4">
         <f t="shared" si="4"/>
-        <v>0.575</v>
+        <v>0.5411764706</v>
       </c>
       <c r="O7" s="4">
         <f t="shared" si="5"/>
-        <v>0.39375</v>
+        <v>0.4235294118</v>
       </c>
       <c r="P7" s="4">
         <f t="shared" si="6"/>
@@ -3361,66 +3454,65 @@
       </c>
       <c r="Q7" s="14">
         <f t="shared" si="7"/>
-        <v>0.08386482814</v>
+        <v>0.07497414288</v>
       </c>
       <c r="R7" s="19">
-        <f t="shared" ref="R7:S7" si="13">R6</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="S7" s="19">
-        <f t="shared" si="13"/>
         <v>1.116</v>
       </c>
       <c r="T7" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.058</v>
       </c>
       <c r="U7" s="19">
         <f t="shared" si="9"/>
-        <v>7.253934856</v>
+        <v>7.636828963</v>
       </c>
       <c r="V7" s="20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AJ7" s="24"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C8" s="14">
-        <v>11.0</v>
+        <v>5.99</v>
       </c>
       <c r="D8" s="15">
-        <f>4.7*454</f>
-        <v>2133.8</v>
+        <f t="shared" ref="D8:D9" si="16">D7</f>
+        <v>454</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="1"/>
-        <v>2.340425532</v>
+        <v>5.99</v>
       </c>
       <c r="F8" s="16">
-        <v>190.0</v>
+        <v>241.0</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="2"/>
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="H8" s="16">
-        <v>112.0</v>
+        <f t="shared" si="10"/>
+        <v>112</v>
       </c>
       <c r="I8" s="18">
         <f t="shared" si="3"/>
-        <v>19.05178571</v>
+        <v>4.053571429</v>
       </c>
       <c r="J8" s="16">
-        <v>23.0</v>
+        <v>21.0</v>
       </c>
       <c r="K8" s="16">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
       <c r="L8" s="16">
         <v>0.0</v>
@@ -3430,11 +3522,11 @@
       </c>
       <c r="N8" s="4">
         <f t="shared" si="4"/>
-        <v>0.4842105263</v>
+        <v>0.3485477178</v>
       </c>
       <c r="O8" s="4">
         <f t="shared" si="5"/>
-        <v>0.4736842105</v>
+        <v>0.6348547718</v>
       </c>
       <c r="P8" s="4">
         <f t="shared" si="6"/>
@@ -3442,74 +3534,67 @@
       </c>
       <c r="Q8" s="14">
         <f t="shared" si="7"/>
-        <v>0.02510320433</v>
-      </c>
-      <c r="R8" s="19"/>
+        <v>0.0703671072</v>
+      </c>
+      <c r="R8" s="19">
+        <f t="shared" ref="R8:S8" si="15">R7</f>
+        <v>1</v>
+      </c>
       <c r="S8" s="19">
-        <v>1.17</v>
+        <f t="shared" si="15"/>
+        <v>1.116</v>
       </c>
       <c r="T8" s="19">
-        <f t="shared" si="11"/>
-        <v>1.17</v>
+        <f t="shared" si="12"/>
+        <v>1.058</v>
       </c>
       <c r="U8" s="19">
         <f t="shared" si="9"/>
-        <v>22.56788848</v>
+        <v>5.240566227</v>
       </c>
       <c r="V8" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="W8" s="26"/>
-      <c r="X8" s="26"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="26"/>
-      <c r="AC8" s="26"/>
-      <c r="AD8" s="26"/>
-      <c r="AE8" s="26"/>
-      <c r="AF8" s="26"/>
-      <c r="AG8" s="26"/>
-      <c r="AH8" s="26"/>
-      <c r="AI8" s="26"/>
-      <c r="AJ8" s="27"/>
+        <v>95</v>
+      </c>
+      <c r="AJ8" s="24"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C9" s="14">
-        <v>3.28</v>
-      </c>
-      <c r="D9" s="25">
-        <f>5*28.3*4</f>
-        <v>566</v>
+        <v>5.49</v>
+      </c>
+      <c r="D9" s="15">
+        <f t="shared" si="16"/>
+        <v>454</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" si="1"/>
-        <v>2.630954064</v>
+        <v>5.49</v>
       </c>
       <c r="F9" s="16">
-        <v>100.0</v>
+        <v>284.0</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="2"/>
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="H9" s="16">
-        <v>113.0</v>
+        <f t="shared" si="10"/>
+        <v>112</v>
       </c>
       <c r="I9" s="18">
-        <v>4.0</v>
+        <f t="shared" si="3"/>
+        <v>4.053571429</v>
       </c>
       <c r="J9" s="16">
-        <v>25.0</v>
+        <v>19.0</v>
       </c>
       <c r="K9" s="16">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="L9" s="16">
         <v>0.0</v>
@@ -3519,11 +3604,11 @@
       </c>
       <c r="N9" s="4">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.2676056338</v>
       </c>
       <c r="O9" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.6971830986</v>
       </c>
       <c r="P9" s="4">
         <f t="shared" si="6"/>
@@ -3531,78 +3616,67 @@
       </c>
       <c r="Q9" s="14">
         <f t="shared" si="7"/>
-        <v>0.0328</v>
+        <v>0.07128217018</v>
       </c>
       <c r="R9" s="19">
-        <v>1.0</v>
+        <f t="shared" ref="R9:S9" si="17">R8</f>
+        <v>1</v>
       </c>
       <c r="S9" s="19">
-        <f>S14</f>
-        <v>1</v>
+        <f t="shared" si="17"/>
+        <v>1.116</v>
       </c>
       <c r="T9" s="19">
-        <f t="shared" si="11"/>
-        <v>1</v>
+        <f t="shared" si="12"/>
+        <v>1.058</v>
       </c>
       <c r="U9" s="19">
         <f t="shared" si="9"/>
-        <v>30.48780488</v>
+        <v>3.971915555</v>
       </c>
       <c r="V9" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="W9" s="21"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21"/>
-      <c r="Z9" s="21"/>
-      <c r="AA9" s="21"/>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="21"/>
-      <c r="AD9" s="21"/>
-      <c r="AE9" s="21"/>
-      <c r="AF9" s="21"/>
-      <c r="AG9" s="21"/>
-      <c r="AH9" s="21"/>
-      <c r="AI9" s="21"/>
-      <c r="AJ9" s="22"/>
+        <v>96</v>
+      </c>
+      <c r="AJ9" s="24"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C10" s="14">
-        <v>3.0</v>
-      </c>
-      <c r="D10" s="25">
-        <f>14.75*28.3</f>
-        <v>417.425</v>
+        <v>9.93</v>
+      </c>
+      <c r="D10" s="15">
+        <f>1.27*454</f>
+        <v>576.58</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="1"/>
-        <v>3.262861592</v>
+        <v>7.818897638</v>
       </c>
       <c r="F10" s="16">
-        <v>120.0</v>
+        <v>160.0</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="2"/>
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="H10" s="16">
-        <v>85.0</v>
+        <f t="shared" si="10"/>
+        <v>112</v>
       </c>
       <c r="I10" s="18">
-        <f>D10/H10</f>
-        <v>4.910882353</v>
+        <f t="shared" si="3"/>
+        <v>5.148035714</v>
       </c>
       <c r="J10" s="16">
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="K10" s="16">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="L10" s="16">
         <v>0.0</v>
@@ -3612,11 +3686,11 @@
       </c>
       <c r="N10" s="4">
         <f t="shared" si="4"/>
-        <v>0.6666666667</v>
+        <v>0.575</v>
       </c>
       <c r="O10" s="4">
         <f t="shared" si="5"/>
-        <v>0.375</v>
+        <v>0.39375</v>
       </c>
       <c r="P10" s="4">
         <f t="shared" si="6"/>
@@ -3624,65 +3698,67 @@
       </c>
       <c r="Q10" s="14">
         <f t="shared" si="7"/>
-        <v>0.03054440918</v>
+        <v>0.08386482814</v>
       </c>
       <c r="R10" s="19">
-        <f>R9</f>
+        <f t="shared" ref="R10:S10" si="18">R7</f>
         <v>1</v>
       </c>
       <c r="S10" s="19">
-        <f>S14</f>
-        <v>1</v>
+        <f t="shared" si="18"/>
+        <v>1.116</v>
       </c>
       <c r="T10" s="19">
-        <f t="shared" si="11"/>
-        <v>1</v>
+        <f t="shared" si="12"/>
+        <v>1.058</v>
       </c>
       <c r="U10" s="19">
         <f t="shared" si="9"/>
-        <v>21.82614379</v>
+        <v>7.253934856</v>
       </c>
       <c r="V10" s="20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AJ10" s="24"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C11" s="14">
-        <v>0.98</v>
-      </c>
-      <c r="D11" s="25">
-        <f>3.75*28.3</f>
-        <v>106.125</v>
+        <v>11.0</v>
+      </c>
+      <c r="D11" s="15">
+        <f>4.7*454</f>
+        <v>2133.8</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" si="1"/>
-        <v>4.192414605</v>
+        <v>2.340425532</v>
       </c>
       <c r="F11" s="16">
-        <v>130.0</v>
+        <v>190.0</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="H11" s="16">
-        <v>70.0</v>
+        <f t="shared" si="10"/>
+        <v>112</v>
       </c>
       <c r="I11" s="18">
-        <v>1.0</v>
+        <f t="shared" si="3"/>
+        <v>19.05178571</v>
       </c>
       <c r="J11" s="16">
-        <v>12.0</v>
+        <v>23.0</v>
       </c>
       <c r="K11" s="16">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="L11" s="16">
         <v>0.0</v>
@@ -3692,11 +3768,11 @@
       </c>
       <c r="N11" s="4">
         <f t="shared" si="4"/>
-        <v>0.3692307692</v>
+        <v>0.4842105263</v>
       </c>
       <c r="O11" s="4">
         <f t="shared" si="5"/>
-        <v>0.6230769231</v>
+        <v>0.4736842105</v>
       </c>
       <c r="P11" s="4">
         <f t="shared" si="6"/>
@@ -3704,66 +3780,78 @@
       </c>
       <c r="Q11" s="14">
         <f t="shared" si="7"/>
-        <v>0.08166666667</v>
+        <v>0.02510320433</v>
       </c>
       <c r="R11" s="19">
-        <f>R9</f>
+        <f>R10</f>
         <v>1</v>
       </c>
       <c r="S11" s="19">
-        <f>S14</f>
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="T11" s="19">
-        <f t="shared" si="11"/>
-        <v>1</v>
+        <f t="shared" si="12"/>
+        <v>1.085</v>
       </c>
       <c r="U11" s="19">
         <f t="shared" si="9"/>
-        <v>4.521193093</v>
+        <v>20.92834103</v>
       </c>
       <c r="V11" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="AJ11" s="24"/>
+        <v>98</v>
+      </c>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="25"/>
+      <c r="AJ11" s="26"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C12" s="14">
-        <v>7.47</v>
-      </c>
-      <c r="D12" s="15">
-        <f>0.75*454</f>
-        <v>340.5</v>
+        <v>3.28</v>
+      </c>
+      <c r="D12" s="27">
+        <f>5*28.3*4</f>
+        <v>566</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="1"/>
-        <v>9.96</v>
+        <v>2.630954064</v>
       </c>
       <c r="F12" s="16">
-        <v>120.0</v>
+        <v>100.0</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" si="2"/>
-        <v>112.5</v>
+        <v>100</v>
       </c>
       <c r="H12" s="16">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="I12" s="18">
-        <f t="shared" ref="I12:I16" si="15">D12/H12</f>
-        <v>3.040178571</v>
+        <f t="shared" si="3"/>
+        <v>5.008849558</v>
       </c>
       <c r="J12" s="16">
-        <v>27.0</v>
+        <v>25.0</v>
       </c>
       <c r="K12" s="16">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="L12" s="16">
         <v>0.0</v>
@@ -3773,11 +3861,11 @@
       </c>
       <c r="N12" s="4">
         <f t="shared" si="4"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O12" s="4">
         <f t="shared" si="5"/>
-        <v>0.0375</v>
+        <v>0</v>
       </c>
       <c r="P12" s="4">
         <f t="shared" si="6"/>
@@ -3785,66 +3873,78 @@
       </c>
       <c r="Q12" s="14">
         <f t="shared" si="7"/>
-        <v>0.09100342633</v>
+        <v>0.02619363958</v>
       </c>
       <c r="R12" s="19">
-        <f t="shared" ref="R12:S12" si="14">R9</f>
+        <v>1.0</v>
+      </c>
+      <c r="S12" s="19">
+        <f>S17</f>
         <v>1</v>
       </c>
-      <c r="S12" s="19">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
       <c r="T12" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="U12" s="19">
         <f t="shared" si="9"/>
-        <v>9.889737522</v>
+        <v>38.17720699</v>
       </c>
       <c r="V12" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ12" s="24"/>
+        <v>100</v>
+      </c>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="21"/>
+      <c r="AC12" s="21"/>
+      <c r="AD12" s="21"/>
+      <c r="AE12" s="21"/>
+      <c r="AF12" s="21"/>
+      <c r="AG12" s="21"/>
+      <c r="AH12" s="21"/>
+      <c r="AI12" s="21"/>
+      <c r="AJ12" s="22"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C13" s="14">
-        <v>8.7</v>
-      </c>
-      <c r="D13" s="25">
-        <f>0.9*454</f>
-        <v>408.6</v>
+        <v>3.0</v>
+      </c>
+      <c r="D13" s="27">
+        <f>14.75*28.3</f>
+        <v>417.425</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" si="1"/>
-        <v>9.666666667</v>
+        <v>3.262861592</v>
       </c>
       <c r="F13" s="16">
-        <v>240.0</v>
+        <v>120.0</v>
       </c>
       <c r="G13" s="17">
         <f t="shared" si="2"/>
-        <v>227</v>
+        <v>125</v>
       </c>
       <c r="H13" s="16">
-        <v>113.0</v>
+        <v>85.0</v>
       </c>
       <c r="I13" s="18">
-        <f t="shared" si="15"/>
-        <v>3.615929204</v>
+        <f t="shared" si="3"/>
+        <v>4.910882353</v>
       </c>
       <c r="J13" s="16">
-        <v>23.0</v>
+        <v>20.0</v>
       </c>
       <c r="K13" s="16">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="L13" s="16">
         <v>0.0</v>
@@ -3854,11 +3954,11 @@
       </c>
       <c r="N13" s="4">
         <f t="shared" si="4"/>
-        <v>0.3833333333</v>
+        <v>0.6666666667</v>
       </c>
       <c r="O13" s="4">
         <f t="shared" si="5"/>
-        <v>0.5625</v>
+        <v>0.375</v>
       </c>
       <c r="P13" s="4">
         <f t="shared" si="6"/>
@@ -3866,66 +3966,66 @@
       </c>
       <c r="Q13" s="14">
         <f t="shared" si="7"/>
-        <v>0.1046095895</v>
+        <v>0.03054440918</v>
       </c>
       <c r="R13" s="19">
-        <f>R9</f>
+        <f>R12</f>
         <v>1</v>
       </c>
       <c r="S13" s="19">
-        <f>S14</f>
+        <f>S17</f>
         <v>1</v>
       </c>
       <c r="T13" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="U13" s="19">
         <f t="shared" si="9"/>
-        <v>3.664418676</v>
+        <v>21.82614379</v>
       </c>
       <c r="V13" s="20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AJ13" s="24"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C14" s="14">
-        <v>10.78</v>
-      </c>
-      <c r="D14" s="25">
-        <f>2*454</f>
-        <v>908</v>
+        <v>0.98</v>
+      </c>
+      <c r="D14" s="27">
+        <f>3.75*28.3</f>
+        <v>106.125</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" si="1"/>
-        <v>5.39</v>
+        <v>4.192414605</v>
       </c>
       <c r="F14" s="16">
-        <v>90.0</v>
+        <v>130.0</v>
       </c>
       <c r="G14" s="17">
         <f t="shared" si="2"/>
-        <v>89.5</v>
+        <v>129</v>
       </c>
       <c r="H14" s="16">
-        <v>112.0</v>
+        <v>70.0</v>
       </c>
       <c r="I14" s="18">
-        <f t="shared" si="15"/>
-        <v>8.107142857</v>
+        <f t="shared" si="3"/>
+        <v>1.516071429</v>
       </c>
       <c r="J14" s="16">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="K14" s="16">
-        <v>1.5</v>
+        <v>9.0</v>
       </c>
       <c r="L14" s="16">
         <v>0.0</v>
@@ -3935,11 +4035,11 @@
       </c>
       <c r="N14" s="4">
         <f t="shared" si="4"/>
-        <v>0.8444444444</v>
+        <v>0.3692307692</v>
       </c>
       <c r="O14" s="4">
         <f t="shared" si="5"/>
-        <v>0.15</v>
+        <v>0.6230769231</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="6"/>
@@ -3947,64 +4047,66 @@
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="7"/>
-        <v>0.06998377</v>
+        <v>0.05386729486</v>
       </c>
       <c r="R14" s="19">
-        <f>R9</f>
+        <f>R12</f>
         <v>1</v>
       </c>
       <c r="S14" s="19">
-        <v>1.0</v>
+        <f>S17</f>
+        <v>1</v>
       </c>
       <c r="T14" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="U14" s="19">
         <f t="shared" si="9"/>
-        <v>12.06628972</v>
+        <v>6.854451671</v>
       </c>
       <c r="V14" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AJ14" s="24"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C15" s="14">
-        <v>7.96</v>
+        <v>7.47</v>
       </c>
       <c r="D15" s="15">
-        <v>454.0</v>
+        <f>0.75*454</f>
+        <v>340.5</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="1"/>
-        <v>7.96</v>
+        <v>9.96</v>
       </c>
       <c r="F15" s="16">
-        <v>80.0</v>
+        <v>120.0</v>
       </c>
       <c r="G15" s="17">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>112.5</v>
       </c>
       <c r="H15" s="16">
         <v>112.0</v>
       </c>
       <c r="I15" s="18">
-        <f t="shared" si="15"/>
-        <v>4.053571429</v>
+        <f t="shared" si="3"/>
+        <v>3.040178571</v>
       </c>
       <c r="J15" s="16">
-        <v>17.0</v>
+        <v>27.0</v>
       </c>
       <c r="K15" s="16">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="L15" s="16">
         <v>0.0</v>
@@ -4014,11 +4116,11 @@
       </c>
       <c r="N15" s="4">
         <f t="shared" si="4"/>
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="O15" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.0375</v>
       </c>
       <c r="P15" s="4">
         <f t="shared" si="6"/>
@@ -4026,894 +4128,870 @@
       </c>
       <c r="Q15" s="14">
         <f t="shared" si="7"/>
-        <v>0.1155117906</v>
+        <v>0.09100342633</v>
       </c>
       <c r="R15" s="19">
-        <f>R9</f>
+        <f t="shared" ref="R15:S15" si="19">R12</f>
         <v>1</v>
       </c>
       <c r="S15" s="19">
-        <f>S14</f>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="T15" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="U15" s="19">
         <f t="shared" si="9"/>
-        <v>7.358556174</v>
+        <v>9.889737522</v>
       </c>
       <c r="V15" s="20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AJ15" s="24"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C16" s="14">
-        <v>2.18</v>
-      </c>
-      <c r="D16" s="25">
-        <f>6.5*28.3</f>
-        <v>183.95</v>
+        <v>8.7</v>
+      </c>
+      <c r="D16" s="27">
+        <f>0.9*454</f>
+        <v>408.6</v>
       </c>
       <c r="E16" s="3">
         <f t="shared" si="1"/>
-        <v>5.380375102</v>
+        <v>9.666666667</v>
       </c>
       <c r="F16" s="16">
-        <v>40.0</v>
+        <v>240.0</v>
       </c>
       <c r="G16" s="17">
         <f t="shared" si="2"/>
-        <v>40.5</v>
+        <v>227</v>
       </c>
       <c r="H16" s="16">
-        <v>85.0</v>
+        <v>113.0</v>
       </c>
       <c r="I16" s="18">
-        <f t="shared" si="15"/>
-        <v>2.164117647</v>
+        <f t="shared" si="3"/>
+        <v>3.615929204</v>
       </c>
       <c r="J16" s="16">
-        <v>5.0</v>
+        <v>23.0</v>
       </c>
       <c r="K16" s="16">
-        <v>0.5</v>
+        <v>15.0</v>
       </c>
       <c r="L16" s="16">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="M16" s="16">
         <v>0.0</v>
       </c>
       <c r="N16" s="4">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.3833333333</v>
       </c>
       <c r="O16" s="4">
         <f t="shared" si="5"/>
-        <v>0.1125</v>
+        <v>0.5625</v>
       </c>
       <c r="P16" s="4">
         <f t="shared" si="6"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="14">
         <f t="shared" si="7"/>
-        <v>0.2014677902</v>
+        <v>0.1046095895</v>
       </c>
       <c r="R16" s="19">
-        <f>R9</f>
+        <f>R12</f>
         <v>1</v>
       </c>
       <c r="S16" s="19">
-        <f>S14</f>
+        <f>S17</f>
         <v>1</v>
       </c>
       <c r="T16" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="U16" s="19">
         <f t="shared" si="9"/>
-        <v>2.481786292</v>
+        <v>3.664418676</v>
       </c>
       <c r="V16" s="20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AJ16" s="24"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C17" s="14">
-        <v>8.98</v>
-      </c>
-      <c r="D17" s="25">
-        <f>7.76*28.3</f>
-        <v>219.608</v>
+        <v>10.78</v>
+      </c>
+      <c r="D17" s="27">
+        <f>2*454</f>
+        <v>908</v>
       </c>
       <c r="E17" s="3">
         <f t="shared" si="1"/>
-        <v>18.56453317</v>
+        <v>5.39</v>
       </c>
       <c r="F17" s="16">
-        <v>120.0</v>
+        <v>90.0</v>
       </c>
       <c r="G17" s="17">
         <f t="shared" si="2"/>
-        <v>113.5</v>
+        <v>89.5</v>
       </c>
       <c r="H17" s="16">
-        <v>84.0</v>
+        <v>112.0</v>
       </c>
       <c r="I17" s="18">
-        <v>1.0</v>
+        <f t="shared" si="3"/>
+        <v>8.107142857</v>
       </c>
       <c r="J17" s="16">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="K17" s="16">
         <v>1.5</v>
       </c>
       <c r="L17" s="16">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="M17" s="16">
         <v>0.0</v>
       </c>
       <c r="N17" s="4">
         <f t="shared" si="4"/>
-        <v>0.7</v>
+        <v>0.8444444444</v>
       </c>
       <c r="O17" s="4">
         <f t="shared" si="5"/>
-        <v>0.1125</v>
+        <v>0.15</v>
       </c>
       <c r="P17" s="4">
         <f t="shared" si="6"/>
-        <v>0.1333333333</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="14">
         <f t="shared" si="7"/>
-        <v>0.4276190476</v>
+        <v>0.06998377</v>
       </c>
       <c r="R17" s="19">
-        <f>R9</f>
+        <f>R12</f>
         <v>1</v>
       </c>
       <c r="S17" s="19">
-        <f>S14</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="T17" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="U17" s="19">
         <f t="shared" si="9"/>
-        <v>1.636971047</v>
+        <v>12.06628972</v>
       </c>
       <c r="V17" s="20" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AJ17" s="24"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C18" s="14">
-        <v>12.94</v>
-      </c>
-      <c r="D18" s="25">
-        <f>2*454</f>
-        <v>908</v>
+        <v>7.96</v>
+      </c>
+      <c r="D18" s="15">
+        <v>454.0</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="1"/>
-        <v>6.47</v>
+        <v>7.96</v>
       </c>
       <c r="F18" s="16">
         <v>80.0</v>
       </c>
       <c r="G18" s="17">
         <f t="shared" si="2"/>
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="H18" s="16">
         <v>112.0</v>
       </c>
       <c r="I18" s="18">
-        <f t="shared" ref="I18:I64" si="16">D18/H18</f>
-        <v>8.107142857</v>
+        <f t="shared" si="3"/>
+        <v>4.053571429</v>
       </c>
       <c r="J18" s="16">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="K18" s="16">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L18" s="16">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="M18" s="16">
         <v>0.0</v>
       </c>
       <c r="N18" s="4">
         <f t="shared" si="4"/>
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O18" s="4">
         <f t="shared" si="5"/>
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="14">
         <f t="shared" si="7"/>
-        <v>0.1064082232</v>
+        <v>0.1155117906</v>
       </c>
       <c r="R18" s="19">
-        <f>R9</f>
+        <f>R12</f>
         <v>1</v>
       </c>
       <c r="S18" s="19">
-        <f>S14</f>
+        <f>S17</f>
         <v>1</v>
       </c>
       <c r="T18" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="U18" s="19">
         <f t="shared" si="9"/>
-        <v>7.048327445</v>
+        <v>7.358556174</v>
       </c>
       <c r="V18" s="20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AJ18" s="24"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C19" s="14">
-        <v>5.46</v>
-      </c>
-      <c r="D19" s="25">
-        <f>12*28.3</f>
-        <v>339.6</v>
+        <v>2.18</v>
+      </c>
+      <c r="D19" s="27">
+        <f>6.5*28.3</f>
+        <v>183.95</v>
       </c>
       <c r="E19" s="3">
         <f t="shared" si="1"/>
-        <v>7.299293286</v>
+        <v>5.380375102</v>
       </c>
       <c r="F19" s="16">
-        <v>70.0</v>
+        <v>40.0</v>
       </c>
       <c r="G19" s="17">
         <f t="shared" si="2"/>
-        <v>69.5</v>
+        <v>40.5</v>
       </c>
       <c r="H19" s="16">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="I19" s="18">
-        <f t="shared" si="16"/>
-        <v>4.042857143</v>
+        <f t="shared" si="3"/>
+        <v>2.164117647</v>
       </c>
       <c r="J19" s="16">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="K19" s="16">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L19" s="16">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="M19" s="16">
         <v>0.0</v>
       </c>
       <c r="N19" s="4">
         <f t="shared" si="4"/>
-        <v>0.6857142857</v>
+        <v>0.5</v>
       </c>
       <c r="O19" s="4">
         <f t="shared" si="5"/>
-        <v>0.1928571429</v>
+        <v>0.1125</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="6"/>
-        <v>0.1142857143</v>
+        <v>0.4</v>
       </c>
       <c r="Q19" s="14">
         <f t="shared" si="7"/>
-        <v>0.1125441696</v>
+        <v>0.2014677902</v>
       </c>
       <c r="R19" s="19">
-        <f>R9</f>
+        <f>R12</f>
         <v>1</v>
       </c>
       <c r="S19" s="19">
-        <f>S14</f>
+        <f>S17</f>
         <v>1</v>
       </c>
       <c r="T19" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="U19" s="19">
         <f t="shared" si="9"/>
-        <v>6.09284593</v>
+        <v>2.481786292</v>
       </c>
       <c r="V19" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="W19" s="26"/>
-      <c r="X19" s="26"/>
-      <c r="Y19" s="26"/>
-      <c r="Z19" s="26"/>
-      <c r="AA19" s="26"/>
-      <c r="AB19" s="26"/>
-      <c r="AC19" s="26"/>
-      <c r="AD19" s="26"/>
-      <c r="AE19" s="26"/>
-      <c r="AF19" s="26"/>
-      <c r="AG19" s="26"/>
-      <c r="AH19" s="26"/>
-      <c r="AI19" s="26"/>
-      <c r="AJ19" s="27"/>
+        <v>107</v>
+      </c>
+      <c r="AJ19" s="24"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C20" s="14">
-        <v>2.33</v>
-      </c>
-      <c r="D20" s="25">
-        <f>56*18</f>
-        <v>1008</v>
+        <v>8.98</v>
+      </c>
+      <c r="D20" s="27">
+        <f>7.76*28.3</f>
+        <v>219.608</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="1"/>
-        <v>1.049424603</v>
+        <v>18.56453317</v>
       </c>
       <c r="F20" s="16">
-        <v>80.0</v>
+        <v>120.0</v>
       </c>
       <c r="G20" s="17">
         <f t="shared" si="2"/>
-        <v>73</v>
-      </c>
-      <c r="H20" s="1">
-        <f>D20/18</f>
-        <v>56</v>
+        <v>113.5</v>
+      </c>
+      <c r="H20" s="16">
+        <v>84.0</v>
       </c>
       <c r="I20" s="18">
-        <f t="shared" si="16"/>
-        <v>18</v>
+        <f t="shared" si="3"/>
+        <v>2.614380952</v>
       </c>
       <c r="J20" s="16">
-        <v>7.0</v>
+        <v>21.0</v>
       </c>
       <c r="K20" s="16">
-        <v>5.0</v>
+        <v>1.5</v>
       </c>
       <c r="L20" s="16">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="M20" s="16">
         <v>0.0</v>
       </c>
       <c r="N20" s="4">
         <f t="shared" si="4"/>
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="O20" s="4">
         <f t="shared" si="5"/>
-        <v>0.5625</v>
+        <v>0.1125</v>
       </c>
       <c r="P20" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.1333333333</v>
       </c>
       <c r="Q20" s="14">
         <f t="shared" si="7"/>
-        <v>0.01849206349</v>
+        <v>0.1635641689</v>
       </c>
       <c r="R20" s="19">
-        <v>1.0</v>
+        <f>R12</f>
+        <v>1</v>
       </c>
       <c r="S20" s="19">
-        <v>1.13</v>
+        <f>S17</f>
+        <v>1</v>
       </c>
       <c r="T20" s="19">
-        <f t="shared" si="11"/>
-        <v>1.065</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="U20" s="19">
         <f t="shared" si="9"/>
-        <v>20.15729614</v>
+        <v>4.279665924</v>
       </c>
       <c r="V20" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="W20" s="21"/>
-      <c r="X20" s="21"/>
-      <c r="Y20" s="21"/>
-      <c r="Z20" s="21"/>
-      <c r="AA20" s="21"/>
-      <c r="AB20" s="21"/>
-      <c r="AC20" s="21"/>
-      <c r="AD20" s="21"/>
-      <c r="AE20" s="21"/>
-      <c r="AF20" s="21"/>
-      <c r="AG20" s="21"/>
-      <c r="AH20" s="21"/>
-      <c r="AI20" s="21"/>
-      <c r="AJ20" s="22"/>
+        <v>108</v>
+      </c>
+      <c r="AJ20" s="24"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C21" s="14">
-        <v>3.98</v>
-      </c>
-      <c r="D21" s="25">
-        <f>32*28.3</f>
-        <v>905.6</v>
+        <v>12.94</v>
+      </c>
+      <c r="D21" s="27">
+        <f>2*454</f>
+        <v>908</v>
       </c>
       <c r="E21" s="3">
         <f t="shared" si="1"/>
-        <v>1.995273852</v>
+        <v>6.47</v>
       </c>
       <c r="F21" s="16">
-        <v>25.0</v>
+        <v>80.0</v>
       </c>
       <c r="G21" s="17">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="H21" s="16">
-        <v>46.0</v>
+        <v>112.0</v>
       </c>
       <c r="I21" s="18">
-        <f t="shared" si="16"/>
-        <v>19.68695652</v>
+        <f t="shared" si="3"/>
+        <v>8.107142857</v>
       </c>
       <c r="J21" s="16">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="K21" s="16">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="L21" s="16">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M21" s="16">
         <v>0.0</v>
       </c>
       <c r="N21" s="4">
         <f t="shared" si="4"/>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="O21" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="6"/>
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="Q21" s="14">
         <f t="shared" si="7"/>
-        <v>0.04043286219</v>
+        <v>0.1064082232</v>
       </c>
       <c r="R21" s="19">
-        <f t="shared" ref="R21:S21" si="17">R20</f>
+        <f>R12</f>
         <v>1</v>
       </c>
       <c r="S21" s="19">
-        <f t="shared" si="17"/>
-        <v>1.13</v>
+        <f>S17</f>
+        <v>1</v>
       </c>
       <c r="T21" s="19">
-        <f t="shared" si="11"/>
-        <v>1.065</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="U21" s="19">
         <f t="shared" si="9"/>
-        <v>21.07196854</v>
+        <v>7.048327445</v>
       </c>
       <c r="V21" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="W21" s="26"/>
-      <c r="X21" s="26"/>
-      <c r="Y21" s="26"/>
-      <c r="Z21" s="26"/>
-      <c r="AA21" s="26"/>
-      <c r="AB21" s="26"/>
-      <c r="AC21" s="26"/>
-      <c r="AD21" s="26"/>
-      <c r="AE21" s="26"/>
-      <c r="AF21" s="26"/>
-      <c r="AG21" s="26"/>
-      <c r="AH21" s="26"/>
-      <c r="AI21" s="26"/>
-      <c r="AJ21" s="27"/>
+        <v>109</v>
+      </c>
+      <c r="AJ21" s="24"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C22" s="14">
-        <v>3.98</v>
-      </c>
-      <c r="D22" s="25">
-        <f>40*28.3</f>
-        <v>1132</v>
+        <v>5.46</v>
+      </c>
+      <c r="D22" s="27">
+        <f>12*28.3</f>
+        <v>339.6</v>
       </c>
       <c r="E22" s="3">
         <f t="shared" si="1"/>
-        <v>1.596219081</v>
+        <v>7.299293286</v>
       </c>
       <c r="F22" s="16">
-        <v>180.0</v>
+        <v>70.0</v>
       </c>
       <c r="G22" s="17">
         <f t="shared" si="2"/>
-        <v>187</v>
+        <v>69.5</v>
       </c>
       <c r="H22" s="16">
-        <v>32.0</v>
+        <v>84.0</v>
       </c>
       <c r="I22" s="18">
-        <f t="shared" si="16"/>
-        <v>35.375</v>
+        <f t="shared" si="3"/>
+        <v>4.042857143</v>
       </c>
       <c r="J22" s="16">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="K22" s="16">
-        <v>15.0</v>
+        <v>1.5</v>
       </c>
       <c r="L22" s="16">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="M22" s="16">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="N22" s="4">
         <f t="shared" si="4"/>
-        <v>0.1555555556</v>
+        <v>0.6857142857</v>
       </c>
       <c r="O22" s="4">
         <f t="shared" si="5"/>
-        <v>0.75</v>
+        <v>0.1928571429</v>
       </c>
       <c r="P22" s="4">
         <f t="shared" si="6"/>
-        <v>0.1777777778</v>
+        <v>0.1142857143</v>
       </c>
       <c r="Q22" s="14">
         <f t="shared" si="7"/>
-        <v>0.01607269056</v>
+        <v>0.1125441696</v>
       </c>
       <c r="R22" s="19">
-        <v>0.509</v>
+        <f>R12</f>
+        <v>1</v>
       </c>
       <c r="S22" s="19">
-        <v>0.434</v>
+        <f>S17</f>
+        <v>1</v>
       </c>
       <c r="T22" s="19">
-        <f t="shared" si="11"/>
-        <v>0.4715</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="U22" s="19">
         <f t="shared" si="9"/>
-        <v>4.563295994</v>
+        <v>6.09284593</v>
       </c>
       <c r="V22" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="21"/>
-      <c r="AA22" s="21"/>
-      <c r="AB22" s="21"/>
-      <c r="AC22" s="21"/>
-      <c r="AD22" s="21"/>
-      <c r="AE22" s="21"/>
-      <c r="AF22" s="21"/>
-      <c r="AG22" s="21"/>
-      <c r="AH22" s="21"/>
-      <c r="AI22" s="21"/>
-      <c r="AJ22" s="22"/>
+        <v>110</v>
+      </c>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="25"/>
+      <c r="AI22" s="25"/>
+      <c r="AJ22" s="26"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C23" s="14">
-        <v>6.57</v>
-      </c>
-      <c r="D23" s="25">
-        <f>36*28.3</f>
-        <v>1018.8</v>
+        <v>2.33</v>
+      </c>
+      <c r="D23" s="27">
+        <f>56*18</f>
+        <v>1008</v>
       </c>
       <c r="E23" s="3">
         <f t="shared" si="1"/>
-        <v>2.927738516</v>
+        <v>1.049424603</v>
       </c>
       <c r="F23" s="16">
-        <v>190.0</v>
+        <v>80.0</v>
       </c>
       <c r="G23" s="17">
         <f t="shared" si="2"/>
-        <v>192</v>
-      </c>
-      <c r="H23" s="16">
-        <v>32.0</v>
+        <v>73</v>
+      </c>
+      <c r="H23" s="1">
+        <f>D23/18</f>
+        <v>56</v>
       </c>
       <c r="I23" s="18">
-        <f t="shared" si="16"/>
-        <v>31.8375</v>
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="J23" s="16">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="K23" s="16">
-        <v>16.0</v>
+        <v>5.0</v>
       </c>
       <c r="L23" s="16">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="M23" s="16">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N23" s="4">
         <f t="shared" si="4"/>
-        <v>0.1684210526</v>
+        <v>0.35</v>
       </c>
       <c r="O23" s="4">
         <f t="shared" si="5"/>
-        <v>0.7578947368</v>
+        <v>0.5625</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="6"/>
-        <v>0.1473684211</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="14">
         <f t="shared" si="7"/>
-        <v>0.025795053</v>
+        <v>0.01849206349</v>
       </c>
       <c r="R23" s="19">
-        <f t="shared" ref="R23:S23" si="18">R22</f>
-        <v>0.509</v>
+        <v>1.0</v>
       </c>
       <c r="S23" s="19">
-        <f t="shared" si="18"/>
-        <v>0.434</v>
+        <v>1.13</v>
       </c>
       <c r="T23" s="19">
-        <f t="shared" si="11"/>
-        <v>0.4715</v>
+        <f t="shared" si="12"/>
+        <v>1.065</v>
       </c>
       <c r="U23" s="19">
         <f t="shared" si="9"/>
-        <v>3.078517664</v>
+        <v>20.15729614</v>
       </c>
       <c r="V23" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ23" s="24"/>
+        <v>112</v>
+      </c>
+      <c r="W23" s="21"/>
+      <c r="X23" s="21"/>
+      <c r="Y23" s="21"/>
+      <c r="Z23" s="21"/>
+      <c r="AA23" s="21"/>
+      <c r="AB23" s="21"/>
+      <c r="AC23" s="21"/>
+      <c r="AD23" s="21"/>
+      <c r="AE23" s="21"/>
+      <c r="AF23" s="21"/>
+      <c r="AG23" s="21"/>
+      <c r="AH23" s="21"/>
+      <c r="AI23" s="21"/>
+      <c r="AJ23" s="22"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C24" s="14">
-        <v>10.48</v>
-      </c>
-      <c r="D24" s="25">
-        <f>30*28.3</f>
-        <v>849</v>
+        <v>3.98</v>
+      </c>
+      <c r="D24" s="27">
+        <f>32*28.3</f>
+        <v>905.6</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="1"/>
-        <v>5.604146054</v>
+        <v>1.995273852</v>
       </c>
       <c r="F24" s="16">
-        <v>50.0</v>
+        <v>25.0</v>
       </c>
       <c r="G24" s="17">
         <f t="shared" si="2"/>
-        <v>49.5</v>
+        <v>24</v>
       </c>
       <c r="H24" s="16">
-        <v>12.0</v>
+        <v>46.0</v>
       </c>
       <c r="I24" s="18">
-        <f t="shared" si="16"/>
-        <v>70.75</v>
+        <f t="shared" si="3"/>
+        <v>19.68695652</v>
       </c>
       <c r="J24" s="16">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="K24" s="16">
-        <v>1.5</v>
+        <v>0.0</v>
       </c>
       <c r="L24" s="16">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="M24" s="16">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="4">
         <f t="shared" si="4"/>
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="O24" s="4">
         <f t="shared" si="5"/>
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="P24" s="4">
         <f t="shared" si="6"/>
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="Q24" s="14">
         <f t="shared" si="7"/>
-        <v>0.02468786808</v>
+        <v>0.04043286219</v>
       </c>
       <c r="R24" s="19">
-        <f t="shared" ref="R24:S24" si="19">R22</f>
-        <v>0.509</v>
+        <f t="shared" ref="R24:S24" si="20">R23</f>
+        <v>1</v>
       </c>
       <c r="S24" s="19">
-        <f t="shared" si="19"/>
-        <v>0.434</v>
+        <f t="shared" si="20"/>
+        <v>1.13</v>
       </c>
       <c r="T24" s="19">
-        <f t="shared" si="11"/>
-        <v>0.4715</v>
+        <f t="shared" si="12"/>
+        <v>1.065</v>
       </c>
       <c r="U24" s="19">
         <f t="shared" si="9"/>
-        <v>9.167255725</v>
+        <v>21.07196854</v>
       </c>
       <c r="V24" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="W24" s="26"/>
-      <c r="X24" s="26"/>
-      <c r="Y24" s="26"/>
-      <c r="Z24" s="26"/>
-      <c r="AA24" s="26"/>
-      <c r="AB24" s="26"/>
-      <c r="AC24" s="26"/>
-      <c r="AD24" s="26"/>
-      <c r="AE24" s="26"/>
-      <c r="AF24" s="26"/>
-      <c r="AG24" s="26"/>
-      <c r="AH24" s="26"/>
-      <c r="AI24" s="26"/>
-      <c r="AJ24" s="27"/>
+        <v>113</v>
+      </c>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="25"/>
+      <c r="AH24" s="25"/>
+      <c r="AI24" s="25"/>
+      <c r="AJ24" s="26"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C25" s="14">
-        <v>50.96</v>
-      </c>
-      <c r="D25" s="15">
-        <v>2268.0</v>
+        <v>3.98</v>
+      </c>
+      <c r="D25" s="27">
+        <f>40*28.3</f>
+        <v>1132</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="1"/>
-        <v>10.20098765</v>
+        <v>1.596219081</v>
       </c>
       <c r="F25" s="16">
-        <v>130.0</v>
+        <v>180.0</v>
       </c>
       <c r="G25" s="17">
         <f t="shared" si="2"/>
-        <v>122.5</v>
+        <v>187</v>
       </c>
       <c r="H25" s="16">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="I25" s="18">
-        <f t="shared" si="16"/>
-        <v>73.16129032</v>
+        <f t="shared" si="3"/>
+        <v>35.375</v>
       </c>
       <c r="J25" s="16">
-        <v>25.0</v>
+        <v>7.0</v>
       </c>
       <c r="K25" s="16">
-        <v>2.5</v>
+        <v>15.0</v>
       </c>
       <c r="L25" s="16">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="M25" s="16">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N25" s="4">
         <f t="shared" si="4"/>
-        <v>0.7692307692</v>
+        <v>0.1555555556</v>
       </c>
       <c r="O25" s="4">
         <f t="shared" si="5"/>
-        <v>0.1730769231</v>
+        <v>0.75</v>
       </c>
       <c r="P25" s="4">
         <f t="shared" si="6"/>
-        <v>0.03076923077</v>
+        <v>0.1777777778</v>
       </c>
       <c r="Q25" s="14">
         <f t="shared" si="7"/>
-        <v>0.0278617284</v>
+        <v>0.01607269056</v>
       </c>
       <c r="R25" s="19">
-        <v>1.0</v>
+        <v>0.509</v>
       </c>
       <c r="S25" s="19">
-        <v>1.18</v>
+        <v>0.434</v>
       </c>
       <c r="T25" s="19">
-        <f t="shared" si="11"/>
-        <v>1.09</v>
+        <f t="shared" si="12"/>
+        <v>0.4715</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="9"/>
-        <v>30.09366564</v>
+        <v>4.563295994</v>
       </c>
       <c r="V25" s="20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="W25" s="21"/>
       <c r="X25" s="21"/>
@@ -4932,291 +5010,316 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C26" s="14">
-        <v>60.26</v>
-      </c>
-      <c r="D26" s="15">
-        <v>2268.0</v>
+        <v>6.57</v>
+      </c>
+      <c r="D26" s="27">
+        <f>36*28.3</f>
+        <v>1018.8</v>
       </c>
       <c r="E26" s="3">
         <f t="shared" si="1"/>
-        <v>12.06262787</v>
+        <v>2.927738516</v>
       </c>
       <c r="F26" s="16">
-        <v>110.0</v>
+        <v>190.0</v>
       </c>
       <c r="G26" s="17">
         <f t="shared" si="2"/>
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="H26" s="16">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="I26" s="18">
-        <f t="shared" si="16"/>
-        <v>75.6</v>
+        <f t="shared" si="3"/>
+        <v>31.8375</v>
       </c>
       <c r="J26" s="16">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
       <c r="K26" s="16">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="L26" s="16">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="M26" s="16">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N26" s="4">
         <f t="shared" si="4"/>
-        <v>0.8727272727</v>
+        <v>0.1684210526</v>
       </c>
       <c r="O26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.7578947368</v>
       </c>
       <c r="P26" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.1473684211</v>
       </c>
       <c r="Q26" s="14">
         <f t="shared" si="7"/>
-        <v>0.03321208113</v>
+        <v>0.025795053</v>
       </c>
       <c r="R26" s="19">
-        <f t="shared" ref="R26:S26" si="20">R25</f>
-        <v>1</v>
+        <f t="shared" ref="R26:S26" si="21">R25</f>
+        <v>0.509</v>
       </c>
       <c r="S26" s="19">
-        <f t="shared" si="20"/>
-        <v>1.18</v>
+        <f t="shared" si="21"/>
+        <v>0.434</v>
       </c>
       <c r="T26" s="19">
-        <f t="shared" si="11"/>
-        <v>1.09</v>
+        <f t="shared" si="12"/>
+        <v>0.4715</v>
       </c>
       <c r="U26" s="19">
         <f t="shared" si="9"/>
-        <v>28.64237033</v>
+        <v>3.078517664</v>
       </c>
       <c r="V26" s="20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AJ26" s="24"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C27" s="14">
-        <v>2.67</v>
-      </c>
-      <c r="D27" s="15">
-        <v>3785.0</v>
+        <v>10.48</v>
+      </c>
+      <c r="D27" s="27">
+        <f>30*28.3</f>
+        <v>849</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" si="1"/>
-        <v>0.3202589168</v>
+        <v>5.604146054</v>
       </c>
       <c r="F27" s="16">
-        <v>90.0</v>
+        <v>50.0</v>
       </c>
       <c r="G27" s="17">
         <f t="shared" si="2"/>
-        <v>84</v>
+        <v>49.5</v>
       </c>
       <c r="H27" s="16">
-        <v>236.6</v>
+        <v>12.0</v>
       </c>
       <c r="I27" s="18">
-        <f t="shared" si="16"/>
-        <v>15.99746407</v>
+        <f t="shared" si="3"/>
+        <v>70.75</v>
       </c>
       <c r="J27" s="16">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="K27" s="16">
-        <v>0.0</v>
+        <v>1.5</v>
       </c>
       <c r="L27" s="16">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="M27" s="16">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N27" s="4">
         <f t="shared" si="4"/>
-        <v>0.3555555556</v>
+        <v>0.48</v>
       </c>
       <c r="O27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="P27" s="4">
         <f t="shared" si="6"/>
-        <v>0.5777777778</v>
+        <v>0.32</v>
       </c>
       <c r="Q27" s="14">
         <f t="shared" si="7"/>
-        <v>0.02086268164</v>
+        <v>0.02468786808</v>
       </c>
       <c r="R27" s="19">
-        <v>1.0</v>
+        <f t="shared" ref="R27:S27" si="22">R25</f>
+        <v>0.509</v>
       </c>
       <c r="S27" s="19">
-        <v>1.14</v>
+        <f t="shared" si="22"/>
+        <v>0.434</v>
       </c>
       <c r="T27" s="19">
-        <f t="shared" si="11"/>
-        <v>1.07</v>
+        <f t="shared" si="12"/>
+        <v>0.4715</v>
       </c>
       <c r="U27" s="19">
         <f t="shared" si="9"/>
-        <v>18.23564444</v>
+        <v>9.167255725</v>
       </c>
       <c r="V27" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="AJ27" s="24"/>
+        <v>117</v>
+      </c>
+      <c r="W27" s="25"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="25"/>
+      <c r="AA27" s="25"/>
+      <c r="AB27" s="25"/>
+      <c r="AC27" s="25"/>
+      <c r="AD27" s="25"/>
+      <c r="AE27" s="25"/>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="25"/>
+      <c r="AH27" s="25"/>
+      <c r="AI27" s="25"/>
+      <c r="AJ27" s="26"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C28" s="14">
-        <v>4.48</v>
-      </c>
-      <c r="D28" s="25">
-        <f>H28*6</f>
-        <v>1419.6</v>
+        <v>50.96</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2268.0</v>
       </c>
       <c r="E28" s="3">
         <f t="shared" si="1"/>
-        <v>1.432741617</v>
+        <v>10.20098765</v>
       </c>
       <c r="F28" s="16">
-        <v>80.0</v>
+        <v>130.0</v>
       </c>
       <c r="G28" s="17">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>122.5</v>
       </c>
       <c r="H28" s="16">
-        <f>H27</f>
-        <v>236.6</v>
+        <v>31.0</v>
       </c>
       <c r="I28" s="18">
-        <f t="shared" si="16"/>
-        <v>6</v>
+        <f t="shared" si="3"/>
+        <v>73.16129032</v>
       </c>
       <c r="J28" s="16">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
       <c r="K28" s="16">
-        <v>0.0</v>
+        <v>2.5</v>
       </c>
       <c r="L28" s="16">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="M28" s="16">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N28" s="4">
         <f t="shared" si="4"/>
-        <v>0.65</v>
+        <v>0.7692307692</v>
       </c>
       <c r="O28" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.1730769231</v>
       </c>
       <c r="P28" s="4">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0.03076923077</v>
       </c>
       <c r="Q28" s="14">
         <f t="shared" si="7"/>
-        <v>0.05743589744</v>
+        <v>0.0278617284</v>
       </c>
       <c r="R28" s="19">
-        <f t="shared" ref="R28:S28" si="21">R27</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="S28" s="19">
-        <f t="shared" si="21"/>
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T28" s="19">
-        <f t="shared" si="11"/>
-        <v>1.07</v>
+        <f t="shared" si="12"/>
+        <v>1.09</v>
       </c>
       <c r="U28" s="19">
         <f t="shared" si="9"/>
-        <v>12.10915179</v>
+        <v>30.09366564</v>
       </c>
       <c r="V28" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="AJ28" s="24"/>
+        <v>119</v>
+      </c>
+      <c r="W28" s="21"/>
+      <c r="X28" s="21"/>
+      <c r="Y28" s="21"/>
+      <c r="Z28" s="21"/>
+      <c r="AA28" s="21"/>
+      <c r="AB28" s="21"/>
+      <c r="AC28" s="21"/>
+      <c r="AD28" s="21"/>
+      <c r="AE28" s="21"/>
+      <c r="AF28" s="21"/>
+      <c r="AG28" s="21"/>
+      <c r="AH28" s="21"/>
+      <c r="AI28" s="21"/>
+      <c r="AJ28" s="22"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C29" s="14">
-        <v>3.54</v>
-      </c>
-      <c r="D29" s="25">
-        <f>32*28.3</f>
-        <v>905.6</v>
+        <v>60.26</v>
+      </c>
+      <c r="D29" s="15">
+        <v>2268.0</v>
       </c>
       <c r="E29" s="3">
         <f t="shared" si="1"/>
-        <v>1.774690813</v>
+        <v>12.06262787</v>
       </c>
       <c r="F29" s="16">
-        <v>100.0</v>
+        <v>110.0</v>
       </c>
       <c r="G29" s="17">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="H29" s="16">
-        <v>170.0</v>
+        <v>30.0</v>
       </c>
       <c r="I29" s="18">
-        <f t="shared" si="16"/>
-        <v>5.327058824</v>
+        <f t="shared" si="3"/>
+        <v>75.6</v>
       </c>
       <c r="J29" s="16">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
       <c r="K29" s="16">
         <v>0.0</v>
       </c>
       <c r="L29" s="16">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="M29" s="16">
         <v>0.0</v>
       </c>
       <c r="N29" s="4">
         <f t="shared" si="4"/>
-        <v>0.68</v>
+        <v>0.8727272727</v>
       </c>
       <c r="O29" s="4">
         <f t="shared" si="5"/>
@@ -5224,80 +5327,79 @@
       </c>
       <c r="P29" s="4">
         <f t="shared" si="6"/>
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="14">
         <f t="shared" si="7"/>
-        <v>0.03909010601</v>
+        <v>0.03321208113</v>
       </c>
       <c r="R29" s="19">
-        <f t="shared" ref="R29:S29" si="22">R27</f>
+        <f t="shared" ref="R29:S29" si="23">R28</f>
         <v>1</v>
       </c>
       <c r="S29" s="19">
-        <f t="shared" si="22"/>
-        <v>1.14</v>
+        <f t="shared" si="23"/>
+        <v>1.18</v>
       </c>
       <c r="T29" s="19">
-        <f t="shared" si="11"/>
-        <v>1.07</v>
+        <f t="shared" si="12"/>
+        <v>1.09</v>
       </c>
       <c r="U29" s="19">
         <f t="shared" si="9"/>
-        <v>18.61340565</v>
+        <v>28.64237033</v>
       </c>
       <c r="V29" s="20" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AJ29" s="24"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C30" s="14">
-        <v>2.94</v>
-      </c>
-      <c r="D30" s="25">
-        <f>24*28.3</f>
-        <v>679.2</v>
+        <v>2.67</v>
+      </c>
+      <c r="D30" s="15">
+        <v>3785.0</v>
       </c>
       <c r="E30" s="3">
         <f t="shared" si="1"/>
-        <v>1.965194346</v>
+        <v>0.3202589168</v>
       </c>
       <c r="F30" s="16">
-        <v>70.0</v>
+        <v>90.0</v>
       </c>
       <c r="G30" s="17">
         <f t="shared" si="2"/>
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H30" s="16">
-        <v>113.0</v>
+        <v>236.6</v>
       </c>
       <c r="I30" s="18">
-        <f t="shared" si="16"/>
-        <v>6.010619469</v>
+        <f t="shared" si="3"/>
+        <v>15.99746407</v>
       </c>
       <c r="J30" s="16">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="K30" s="16">
         <v>0.0</v>
       </c>
       <c r="L30" s="16">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="M30" s="16">
         <v>0.0</v>
       </c>
       <c r="N30" s="4">
         <f t="shared" si="4"/>
-        <v>0.6857142857</v>
+        <v>0.3555555556</v>
       </c>
       <c r="O30" s="4">
         <f t="shared" si="5"/>
@@ -5305,95 +5407,94 @@
       </c>
       <c r="P30" s="4">
         <f t="shared" si="6"/>
-        <v>0.3428571429</v>
+        <v>0.5777777778</v>
       </c>
       <c r="Q30" s="14">
         <f t="shared" si="7"/>
-        <v>0.04076118963</v>
+        <v>0.02086268164</v>
       </c>
       <c r="R30" s="19">
-        <f t="shared" ref="R30:S30" si="23">R27</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="S30" s="19">
-        <f t="shared" si="23"/>
         <v>1.14</v>
       </c>
       <c r="T30" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.07</v>
       </c>
       <c r="U30" s="19">
         <f t="shared" si="9"/>
-        <v>18.0003158</v>
+        <v>18.23564444</v>
       </c>
       <c r="V30" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ30" s="24"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C31" s="14">
-        <v>2.74</v>
-      </c>
-      <c r="D31" s="25">
-        <f>6*28.3</f>
-        <v>169.8</v>
+        <v>4.48</v>
+      </c>
+      <c r="D31" s="27">
+        <f>H31*6</f>
+        <v>1419.6</v>
       </c>
       <c r="E31" s="3">
         <f t="shared" si="1"/>
-        <v>7.326030624</v>
+        <v>1.432741617</v>
       </c>
       <c r="F31" s="16">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
       <c r="G31" s="17">
         <f t="shared" si="2"/>
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H31" s="16">
-        <v>28.0</v>
+        <f>H30</f>
+        <v>236.6</v>
       </c>
       <c r="I31" s="18">
-        <f t="shared" si="16"/>
-        <v>6.064285714</v>
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="J31" s="16">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="K31" s="16">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="L31" s="16">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="M31" s="16">
         <v>0.0</v>
       </c>
       <c r="N31" s="4">
         <f t="shared" si="4"/>
-        <v>0.2857142857</v>
+        <v>0.65</v>
       </c>
       <c r="O31" s="4">
         <f t="shared" si="5"/>
-        <v>0.6428571429</v>
+        <v>0</v>
       </c>
       <c r="P31" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q31" s="14">
         <f t="shared" si="7"/>
-        <v>0.09036513545</v>
+        <v>0.05743589744</v>
       </c>
       <c r="R31" s="19">
-        <f t="shared" ref="R31:S31" si="24">R27</f>
+        <f t="shared" ref="R31:S31" si="24">R30</f>
         <v>1</v>
       </c>
       <c r="S31" s="19">
@@ -5401,169 +5502,146 @@
         <v>1.14</v>
       </c>
       <c r="T31" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.07</v>
       </c>
       <c r="U31" s="19">
         <f t="shared" si="9"/>
-        <v>3.383099955</v>
+        <v>12.10915179</v>
       </c>
       <c r="V31" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="W31" s="26"/>
-      <c r="X31" s="26"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="26"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="26"/>
-      <c r="AC31" s="26"/>
-      <c r="AD31" s="26"/>
-      <c r="AE31" s="26"/>
-      <c r="AF31" s="26"/>
-      <c r="AG31" s="26"/>
-      <c r="AH31" s="26"/>
-      <c r="AI31" s="26"/>
-      <c r="AJ31" s="27"/>
+        <v>122</v>
+      </c>
+      <c r="AJ31" s="24"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C32" s="14">
-        <v>0.82</v>
-      </c>
-      <c r="D32" s="25">
-        <f>15.5*28.3</f>
-        <v>438.65</v>
+        <v>3.54</v>
+      </c>
+      <c r="D32" s="27">
+        <f>32*28.3</f>
+        <v>905.6</v>
       </c>
       <c r="E32" s="3">
         <f t="shared" si="1"/>
-        <v>0.8486948592</v>
+        <v>1.774690813</v>
       </c>
       <c r="F32" s="16">
-        <v>110.0</v>
+        <v>100.0</v>
       </c>
       <c r="G32" s="17">
         <f t="shared" si="2"/>
-        <v>84.5</v>
+        <v>96</v>
       </c>
       <c r="H32" s="16">
-        <v>130.0</v>
+        <v>170.0</v>
       </c>
       <c r="I32" s="18">
-        <f t="shared" si="16"/>
-        <v>3.374230769</v>
+        <f t="shared" si="3"/>
+        <v>5.327058824</v>
       </c>
       <c r="J32" s="16">
-        <v>6.0</v>
+        <v>17.0</v>
       </c>
       <c r="K32" s="16">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="L32" s="16">
-        <v>20.0</v>
+        <v>7.0</v>
       </c>
       <c r="M32" s="16">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="N32" s="4">
         <f t="shared" si="4"/>
-        <v>0.2181818182</v>
+        <v>0.68</v>
       </c>
       <c r="O32" s="4">
         <f t="shared" si="5"/>
-        <v>0.04090909091</v>
+        <v>0</v>
       </c>
       <c r="P32" s="4">
         <f t="shared" si="6"/>
-        <v>0.7272727273</v>
+        <v>0.28</v>
       </c>
       <c r="Q32" s="14">
         <f t="shared" si="7"/>
-        <v>0.04050305863</v>
+        <v>0.03909010601</v>
       </c>
       <c r="R32" s="19">
-        <f>AVERAGE(0.7,0.89)</f>
-        <v>0.795</v>
-      </c>
-      <c r="S32" s="19"/>
+        <f t="shared" ref="R32:S32" si="25">R30</f>
+        <v>1</v>
+      </c>
+      <c r="S32" s="19">
+        <f t="shared" si="25"/>
+        <v>1.14</v>
+      </c>
       <c r="T32" s="19">
-        <f t="shared" si="11"/>
-        <v>0.795</v>
+        <f t="shared" si="12"/>
+        <v>1.07</v>
       </c>
       <c r="U32" s="19">
         <f t="shared" si="9"/>
-        <v>4.282504861</v>
+        <v>18.61340565</v>
       </c>
       <c r="V32" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="W32" s="21"/>
-      <c r="X32" s="21"/>
-      <c r="Y32" s="21"/>
-      <c r="Z32" s="21"/>
-      <c r="AA32" s="21"/>
-      <c r="AB32" s="21"/>
-      <c r="AC32" s="21"/>
-      <c r="AD32" s="21"/>
-      <c r="AE32" s="21"/>
-      <c r="AF32" s="21"/>
-      <c r="AG32" s="21"/>
-      <c r="AH32" s="21"/>
-      <c r="AI32" s="21"/>
-      <c r="AJ32" s="22"/>
+        <v>123</v>
+      </c>
+      <c r="AJ32" s="24"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C33" s="14">
-        <v>0.82</v>
-      </c>
-      <c r="D33" s="25">
-        <f>15.25*28.3</f>
-        <v>431.575</v>
+        <v>2.94</v>
+      </c>
+      <c r="D33" s="27">
+        <f>24*28.3</f>
+        <v>679.2</v>
       </c>
       <c r="E33" s="3">
         <f t="shared" si="1"/>
-        <v>0.8626078897</v>
+        <v>1.965194346</v>
       </c>
       <c r="F33" s="16">
-        <v>120.0</v>
+        <v>70.0</v>
       </c>
       <c r="G33" s="17">
         <f t="shared" si="2"/>
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H33" s="16">
-        <v>130.0</v>
+        <v>113.0</v>
       </c>
       <c r="I33" s="18">
-        <f t="shared" si="16"/>
-        <v>3.319807692</v>
+        <f t="shared" si="3"/>
+        <v>6.010619469</v>
       </c>
       <c r="J33" s="16">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="K33" s="16">
         <v>0.0</v>
       </c>
       <c r="L33" s="16">
-        <v>22.0</v>
+        <v>6.0</v>
       </c>
       <c r="M33" s="16">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="N33" s="4">
         <f t="shared" si="4"/>
-        <v>0.2666666667</v>
+        <v>0.6857142857</v>
       </c>
       <c r="O33" s="4">
         <f t="shared" si="5"/>
@@ -5571,124 +5649,139 @@
       </c>
       <c r="P33" s="4">
         <f t="shared" si="6"/>
-        <v>0.7333333333</v>
+        <v>0.3428571429</v>
       </c>
       <c r="Q33" s="14">
         <f t="shared" si="7"/>
-        <v>0.0308752824</v>
+        <v>0.04076118963</v>
       </c>
       <c r="R33" s="19">
-        <f t="shared" ref="R33:S33" si="25">R32</f>
-        <v>0.795</v>
-      </c>
-      <c r="S33" s="19" t="str">
-        <f t="shared" si="25"/>
-        <v/>
+        <f t="shared" ref="R33:S33" si="26">R30</f>
+        <v>1</v>
+      </c>
+      <c r="S33" s="19">
+        <f t="shared" si="26"/>
+        <v>1.14</v>
       </c>
       <c r="T33" s="19">
-        <f t="shared" si="11"/>
-        <v>0.795</v>
+        <f t="shared" si="12"/>
+        <v>1.07</v>
       </c>
       <c r="U33" s="19">
         <f t="shared" si="9"/>
-        <v>6.866333959</v>
+        <v>18.0003158</v>
       </c>
       <c r="V33" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AJ33" s="24"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C34" s="14">
-        <v>0.82</v>
-      </c>
-      <c r="D34" s="25">
-        <f t="shared" ref="D34:D36" si="26">15.5*28.3</f>
-        <v>438.65</v>
+        <v>2.74</v>
+      </c>
+      <c r="D34" s="27">
+        <f>6*28.3</f>
+        <v>169.8</v>
       </c>
       <c r="E34" s="3">
         <f t="shared" si="1"/>
-        <v>0.8486948592</v>
+        <v>7.326030624</v>
       </c>
       <c r="F34" s="16">
-        <v>120.0</v>
+        <v>70.0</v>
       </c>
       <c r="G34" s="17">
         <f t="shared" si="2"/>
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="H34" s="16">
-        <v>130.0</v>
+        <v>28.0</v>
       </c>
       <c r="I34" s="18">
-        <f t="shared" si="16"/>
-        <v>3.374230769</v>
+        <f t="shared" si="3"/>
+        <v>6.064285714</v>
       </c>
       <c r="J34" s="16">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="K34" s="16">
+        <v>5.0</v>
+      </c>
+      <c r="L34" s="16">
         <v>0.0</v>
       </c>
-      <c r="L34" s="16">
-        <v>21.0</v>
-      </c>
       <c r="M34" s="16">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="N34" s="4">
         <f t="shared" si="4"/>
-        <v>0.2333333333</v>
+        <v>0.2857142857</v>
       </c>
       <c r="O34" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.6428571429</v>
       </c>
       <c r="P34" s="4">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="14">
         <f t="shared" si="7"/>
-        <v>0.03471690739</v>
+        <v>0.09036513545</v>
       </c>
       <c r="R34" s="19">
-        <v>0.648</v>
+        <f t="shared" ref="R34:S34" si="27">R30</f>
+        <v>1</v>
       </c>
       <c r="S34" s="19">
-        <v>0.588</v>
+        <f t="shared" si="27"/>
+        <v>1.14</v>
       </c>
       <c r="T34" s="19">
-        <f t="shared" si="11"/>
-        <v>0.618</v>
+        <f t="shared" si="12"/>
+        <v>1.07</v>
       </c>
       <c r="U34" s="19">
         <f t="shared" si="9"/>
-        <v>4.153595779</v>
+        <v>3.383099955</v>
       </c>
       <c r="V34" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ34" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="W34" s="25"/>
+      <c r="X34" s="25"/>
+      <c r="Y34" s="25"/>
+      <c r="Z34" s="25"/>
+      <c r="AA34" s="25"/>
+      <c r="AB34" s="25"/>
+      <c r="AC34" s="25"/>
+      <c r="AD34" s="25"/>
+      <c r="AE34" s="25"/>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="25"/>
+      <c r="AH34" s="25"/>
+      <c r="AI34" s="25"/>
+      <c r="AJ34" s="26"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C35" s="14">
         <v>0.82</v>
       </c>
-      <c r="D35" s="25">
-        <f t="shared" si="26"/>
+      <c r="D35" s="27">
+        <f>15.5*28.3</f>
         <v>438.65</v>
       </c>
       <c r="E35" s="3">
@@ -5700,173 +5793,186 @@
       </c>
       <c r="G35" s="17">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>84.5</v>
       </c>
       <c r="H35" s="16">
         <v>130.0</v>
       </c>
       <c r="I35" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="3"/>
         <v>3.374230769</v>
       </c>
       <c r="J35" s="16">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="K35" s="16">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="L35" s="16">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="M35" s="16">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="N35" s="4">
         <f t="shared" si="4"/>
-        <v>0.2545454545</v>
+        <v>0.2181818182</v>
       </c>
       <c r="O35" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.04090909091</v>
       </c>
       <c r="P35" s="4">
         <f t="shared" si="6"/>
-        <v>0.6909090909</v>
+        <v>0.7272727273</v>
       </c>
       <c r="Q35" s="14">
         <f t="shared" si="7"/>
-        <v>0.03471690739</v>
+        <v>0.04050305863</v>
       </c>
       <c r="R35" s="19">
-        <f t="shared" ref="R35:S35" si="27">R34</f>
-        <v>0.648</v>
-      </c>
-      <c r="S35" s="19">
-        <f t="shared" si="27"/>
-        <v>0.588</v>
-      </c>
+        <f>AVERAGE(0.7,0.89)</f>
+        <v>0.795</v>
+      </c>
+      <c r="S35" s="19"/>
       <c r="T35" s="19">
-        <f t="shared" si="11"/>
-        <v>0.618</v>
+        <f t="shared" si="12"/>
+        <v>0.795</v>
       </c>
       <c r="U35" s="19">
         <f t="shared" si="9"/>
-        <v>4.531195395</v>
+        <v>4.282504861</v>
       </c>
       <c r="V35" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ35" s="24"/>
+        <v>127</v>
+      </c>
+      <c r="W35" s="21"/>
+      <c r="X35" s="21"/>
+      <c r="Y35" s="21"/>
+      <c r="Z35" s="21"/>
+      <c r="AA35" s="21"/>
+      <c r="AB35" s="21"/>
+      <c r="AC35" s="21"/>
+      <c r="AD35" s="21"/>
+      <c r="AE35" s="21"/>
+      <c r="AF35" s="21"/>
+      <c r="AG35" s="21"/>
+      <c r="AH35" s="21"/>
+      <c r="AI35" s="21"/>
+      <c r="AJ35" s="22"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C36" s="14">
         <v>0.82</v>
       </c>
-      <c r="D36" s="25">
-        <f t="shared" si="26"/>
-        <v>438.65</v>
+      <c r="D36" s="27">
+        <f>15.25*28.3</f>
+        <v>431.575</v>
       </c>
       <c r="E36" s="3">
         <f t="shared" si="1"/>
-        <v>0.8486948592</v>
+        <v>0.8626078897</v>
       </c>
       <c r="F36" s="16">
         <v>120.0</v>
       </c>
       <c r="G36" s="17">
         <f t="shared" si="2"/>
-        <v>94.5</v>
+        <v>84</v>
       </c>
       <c r="H36" s="16">
         <v>130.0</v>
       </c>
       <c r="I36" s="18">
-        <f t="shared" si="16"/>
-        <v>3.374230769</v>
+        <f t="shared" si="3"/>
+        <v>3.319807692</v>
       </c>
       <c r="J36" s="16">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="K36" s="16">
-        <v>2.5</v>
+        <v>0.0</v>
       </c>
       <c r="L36" s="16">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="M36" s="16">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="N36" s="4">
         <f t="shared" si="4"/>
-        <v>0.2</v>
+        <v>0.2666666667</v>
       </c>
       <c r="O36" s="4">
         <f t="shared" si="5"/>
-        <v>0.1875</v>
+        <v>0</v>
       </c>
       <c r="P36" s="4">
         <f t="shared" si="6"/>
-        <v>0.6</v>
+        <v>0.7333333333</v>
       </c>
       <c r="Q36" s="14">
         <f t="shared" si="7"/>
-        <v>0.04050305863</v>
+        <v>0.0308752824</v>
       </c>
       <c r="R36" s="19">
-        <v>0.74</v>
-      </c>
-      <c r="S36" s="19">
-        <v>0.83</v>
+        <f t="shared" ref="R36:S36" si="28">R35</f>
+        <v>0.795</v>
+      </c>
+      <c r="S36" s="19" t="str">
+        <f t="shared" si="28"/>
+        <v/>
       </c>
       <c r="T36" s="19">
-        <f t="shared" si="11"/>
-        <v>0.785</v>
+        <f t="shared" si="12"/>
+        <v>0.795</v>
       </c>
       <c r="U36" s="19">
         <f t="shared" si="9"/>
-        <v>3.876250469</v>
+        <v>6.866333959</v>
       </c>
       <c r="V36" s="20" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AJ36" s="24"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C37" s="14">
-        <v>1.24</v>
-      </c>
-      <c r="D37" s="15">
-        <v>454.0</v>
+        <v>0.82</v>
+      </c>
+      <c r="D37" s="27">
+        <f t="shared" ref="D37:D39" si="29">15.5*28.3</f>
+        <v>438.65</v>
       </c>
       <c r="E37" s="3">
         <f t="shared" si="1"/>
-        <v>1.24</v>
+        <v>0.8486948592</v>
       </c>
       <c r="F37" s="16">
-        <v>100.0</v>
+        <v>120.0</v>
       </c>
       <c r="G37" s="17">
         <f t="shared" si="2"/>
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H37" s="16">
-        <v>35.0</v>
+        <v>130.0</v>
       </c>
       <c r="I37" s="18">
-        <f t="shared" si="16"/>
-        <v>12.97142857</v>
+        <f t="shared" si="3"/>
+        <v>3.374230769</v>
       </c>
       <c r="J37" s="16">
         <v>7.0</v>
@@ -5875,14 +5981,14 @@
         <v>0.0</v>
       </c>
       <c r="L37" s="16">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="M37" s="16">
         <v>5.0</v>
       </c>
       <c r="N37" s="4">
         <f t="shared" si="4"/>
-        <v>0.28</v>
+        <v>0.2333333333</v>
       </c>
       <c r="O37" s="4">
         <f t="shared" si="5"/>
@@ -5890,79 +5996,78 @@
       </c>
       <c r="P37" s="4">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="Q37" s="14">
         <f t="shared" si="7"/>
-        <v>0.01365638767</v>
+        <v>0.03471690739</v>
       </c>
       <c r="R37" s="19">
-        <f t="shared" ref="R37:S37" si="28">R32</f>
-        <v>0.795</v>
-      </c>
-      <c r="S37" s="19" t="str">
-        <f t="shared" si="28"/>
-        <v/>
+        <v>0.648</v>
+      </c>
+      <c r="S37" s="19">
+        <v>0.588</v>
       </c>
       <c r="T37" s="19">
-        <f t="shared" si="11"/>
-        <v>0.795</v>
+        <f t="shared" si="12"/>
+        <v>0.618</v>
       </c>
       <c r="U37" s="19">
         <f t="shared" si="9"/>
-        <v>16.30006452</v>
-      </c>
-      <c r="V37" s="23" t="s">
-        <v>126</v>
+        <v>4.153595779</v>
+      </c>
+      <c r="V37" s="20" t="s">
+        <v>129</v>
       </c>
       <c r="AJ37" s="24"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C38" s="14">
-        <v>1.76</v>
-      </c>
-      <c r="D38" s="15">
-        <v>454.0</v>
+        <v>0.82</v>
+      </c>
+      <c r="D38" s="27">
+        <f t="shared" si="29"/>
+        <v>438.65</v>
       </c>
       <c r="E38" s="3">
         <f t="shared" si="1"/>
-        <v>1.76</v>
+        <v>0.8486948592</v>
       </c>
       <c r="F38" s="16">
-        <v>100.0</v>
+        <v>110.0</v>
       </c>
       <c r="G38" s="17">
         <f t="shared" si="2"/>
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="H38" s="16">
-        <v>35.0</v>
+        <v>130.0</v>
       </c>
       <c r="I38" s="18">
-        <f t="shared" si="16"/>
-        <v>12.97142857</v>
+        <f t="shared" si="3"/>
+        <v>3.374230769</v>
       </c>
       <c r="J38" s="16">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="K38" s="16">
         <v>0.0</v>
       </c>
       <c r="L38" s="16">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
       <c r="M38" s="16">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="N38" s="4">
         <f t="shared" si="4"/>
-        <v>0.32</v>
+        <v>0.2545454545</v>
       </c>
       <c r="O38" s="4">
         <f t="shared" si="5"/>
@@ -5970,159 +6075,158 @@
       </c>
       <c r="P38" s="4">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>0.6909090909</v>
       </c>
       <c r="Q38" s="14">
         <f t="shared" si="7"/>
-        <v>0.01696035242</v>
+        <v>0.03471690739</v>
       </c>
       <c r="R38" s="19">
-        <f t="shared" ref="R38:S38" si="29">R32</f>
-        <v>0.795</v>
-      </c>
-      <c r="S38" s="19" t="str">
-        <f t="shared" si="29"/>
-        <v/>
+        <f t="shared" ref="R38:S38" si="30">R37</f>
+        <v>0.648</v>
+      </c>
+      <c r="S38" s="19">
+        <f t="shared" si="30"/>
+        <v>0.588</v>
       </c>
       <c r="T38" s="19">
-        <f t="shared" si="11"/>
-        <v>0.795</v>
+        <f t="shared" si="12"/>
+        <v>0.618</v>
       </c>
       <c r="U38" s="19">
         <f t="shared" si="9"/>
-        <v>14.99968831</v>
+        <v>4.531195395</v>
       </c>
       <c r="V38" s="20" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AJ38" s="24"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C39" s="14">
-        <v>1.87</v>
-      </c>
-      <c r="D39" s="15">
-        <v>454.0</v>
+        <v>0.82</v>
+      </c>
+      <c r="D39" s="27">
+        <f t="shared" si="29"/>
+        <v>438.65</v>
       </c>
       <c r="E39" s="3">
         <f t="shared" si="1"/>
-        <v>1.87</v>
+        <v>0.8486948592</v>
       </c>
       <c r="F39" s="16">
-        <v>80.0</v>
+        <v>120.0</v>
       </c>
       <c r="G39" s="17">
         <f t="shared" si="2"/>
-        <v>76.5</v>
+        <v>94.5</v>
       </c>
       <c r="H39" s="16">
-        <v>35.0</v>
+        <v>130.0</v>
       </c>
       <c r="I39" s="18">
-        <f t="shared" si="16"/>
-        <v>12.97142857</v>
+        <f t="shared" si="3"/>
+        <v>3.374230769</v>
       </c>
       <c r="J39" s="16">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="K39" s="16">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L39" s="16">
-        <v>21.0</v>
+        <v>18.0</v>
       </c>
       <c r="M39" s="16">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="N39" s="4">
         <f t="shared" si="4"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="O39" s="4">
         <f t="shared" si="5"/>
-        <v>0.05625</v>
+        <v>0.1875</v>
       </c>
       <c r="P39" s="4">
         <f t="shared" si="6"/>
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="Q39" s="14">
         <f t="shared" si="7"/>
-        <v>0.01802037445</v>
+        <v>0.04050305863</v>
       </c>
       <c r="R39" s="19">
-        <f t="shared" ref="R39:S39" si="30">R34</f>
-        <v>0.648</v>
+        <v>0.74</v>
       </c>
       <c r="S39" s="19">
-        <f t="shared" si="30"/>
-        <v>0.588</v>
+        <v>0.83</v>
       </c>
       <c r="T39" s="19">
-        <f t="shared" si="11"/>
-        <v>0.618</v>
+        <f t="shared" si="12"/>
+        <v>0.785</v>
       </c>
       <c r="U39" s="19">
         <f t="shared" si="9"/>
-        <v>13.71780596</v>
+        <v>3.876250469</v>
       </c>
       <c r="V39" s="20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AJ39" s="24"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C40" s="14">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="D40" s="15">
         <v>454.0</v>
       </c>
       <c r="E40" s="3">
         <f t="shared" si="1"/>
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="F40" s="16">
-        <v>90.0</v>
+        <v>100.0</v>
       </c>
       <c r="G40" s="17">
         <f t="shared" si="2"/>
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="H40" s="16">
         <v>35.0</v>
       </c>
       <c r="I40" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="3"/>
         <v>12.97142857</v>
       </c>
       <c r="J40" s="16">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="K40" s="16">
         <v>0.0</v>
       </c>
       <c r="L40" s="16">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="M40" s="16">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="N40" s="4">
         <f t="shared" si="4"/>
-        <v>0.3555555556</v>
+        <v>0.28</v>
       </c>
       <c r="O40" s="4">
         <f t="shared" si="5"/>
@@ -6130,225 +6234,226 @@
       </c>
       <c r="P40" s="4">
         <f t="shared" si="6"/>
-        <v>0.9333333333</v>
+        <v>0.88</v>
       </c>
       <c r="Q40" s="14">
         <f t="shared" si="7"/>
-        <v>0.01850220264</v>
+        <v>0.01365638767</v>
       </c>
       <c r="R40" s="19">
-        <f>R34</f>
-        <v>0.648</v>
-      </c>
-      <c r="S40" s="19">
-        <f>S35</f>
-        <v>0.588</v>
+        <f t="shared" ref="R40:S40" si="31">R35</f>
+        <v>0.795</v>
+      </c>
+      <c r="S40" s="19" t="str">
+        <f t="shared" si="31"/>
+        <v/>
       </c>
       <c r="T40" s="19">
-        <f t="shared" si="11"/>
-        <v>0.618</v>
+        <f t="shared" si="12"/>
+        <v>0.795</v>
       </c>
       <c r="U40" s="19">
         <f t="shared" si="9"/>
-        <v>11.87606349</v>
-      </c>
-      <c r="V40" s="20" t="s">
-        <v>129</v>
+        <v>16.30006452</v>
+      </c>
+      <c r="V40" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="AJ40" s="24"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C41" s="14">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="D41" s="15">
         <v>454.0</v>
       </c>
       <c r="E41" s="3">
         <f t="shared" si="1"/>
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="F41" s="16">
-        <v>120.0</v>
+        <v>100.0</v>
       </c>
       <c r="G41" s="17">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="H41" s="16">
         <v>35.0</v>
       </c>
       <c r="I41" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="3"/>
         <v>12.97142857</v>
       </c>
       <c r="J41" s="16">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="K41" s="16">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L41" s="16">
         <v>22.0</v>
       </c>
       <c r="M41" s="16">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="N41" s="4">
         <f t="shared" si="4"/>
-        <v>0.2333333333</v>
+        <v>0.32</v>
       </c>
       <c r="O41" s="4">
         <f t="shared" si="5"/>
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="P41" s="4">
         <f t="shared" si="6"/>
-        <v>0.7333333333</v>
+        <v>0.88</v>
       </c>
       <c r="Q41" s="14">
         <f t="shared" si="7"/>
-        <v>0.01607929515</v>
+        <v>0.01696035242</v>
       </c>
       <c r="R41" s="19">
-        <f t="shared" ref="R41:S41" si="31">R36</f>
-        <v>0.74</v>
-      </c>
-      <c r="S41" s="19">
-        <f t="shared" si="31"/>
-        <v>0.83</v>
+        <f t="shared" ref="R41:S41" si="32">R35</f>
+        <v>0.795</v>
+      </c>
+      <c r="S41" s="19" t="str">
+        <f t="shared" si="32"/>
+        <v/>
       </c>
       <c r="T41" s="19">
-        <f t="shared" si="11"/>
-        <v>0.785</v>
+        <f t="shared" si="12"/>
+        <v>0.795</v>
       </c>
       <c r="U41" s="19">
         <f t="shared" si="9"/>
-        <v>11.39146119</v>
+        <v>14.99968831</v>
       </c>
       <c r="V41" s="20" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AJ41" s="24"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C42" s="14">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="D42" s="15">
         <v>454.0</v>
       </c>
       <c r="E42" s="3">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="F42" s="16">
-        <v>130.0</v>
+        <v>80.0</v>
       </c>
       <c r="G42" s="17">
         <f t="shared" si="2"/>
-        <v>119</v>
+        <v>76.5</v>
       </c>
       <c r="H42" s="16">
-        <v>91.0</v>
+        <v>35.0</v>
       </c>
       <c r="I42" s="18">
-        <f t="shared" si="16"/>
-        <v>4.989010989</v>
+        <f t="shared" si="3"/>
+        <v>12.97142857</v>
       </c>
       <c r="J42" s="16">
-        <v>14.0</v>
+        <v>8.0</v>
       </c>
       <c r="K42" s="16">
-        <v>7.0</v>
+        <v>0.5</v>
       </c>
       <c r="L42" s="16">
-        <v>2.0</v>
+        <v>21.0</v>
       </c>
       <c r="M42" s="16">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="N42" s="4">
         <f t="shared" si="4"/>
-        <v>0.4307692308</v>
+        <v>0.4</v>
       </c>
       <c r="O42" s="4">
         <f t="shared" si="5"/>
-        <v>0.4846153846</v>
+        <v>0.05625</v>
       </c>
       <c r="P42" s="4">
         <f t="shared" si="6"/>
-        <v>0.06153846154</v>
+        <v>1.05</v>
       </c>
       <c r="Q42" s="14">
         <f t="shared" si="7"/>
-        <v>0.02147577093</v>
+        <v>0.01802037445</v>
       </c>
       <c r="R42" s="19">
-        <v>0.7</v>
+        <f t="shared" ref="R42:S42" si="33">R37</f>
+        <v>0.648</v>
       </c>
       <c r="S42" s="19">
-        <v>0.97</v>
+        <f t="shared" si="33"/>
+        <v>0.588</v>
       </c>
       <c r="T42" s="19">
-        <f t="shared" si="11"/>
-        <v>0.835</v>
+        <f t="shared" si="12"/>
+        <v>0.618</v>
       </c>
       <c r="U42" s="19">
         <f t="shared" si="9"/>
-        <v>16.74874951</v>
+        <v>13.71780596</v>
       </c>
       <c r="V42" s="20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AJ42" s="24"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C43" s="14">
-        <v>1.16</v>
-      </c>
-      <c r="D43" s="25">
-        <f>15*28.3</f>
-        <v>424.5</v>
+        <v>1.92</v>
+      </c>
+      <c r="D43" s="15">
+        <v>454.0</v>
       </c>
       <c r="E43" s="3">
         <f t="shared" si="1"/>
-        <v>1.240612485</v>
+        <v>1.92</v>
       </c>
       <c r="F43" s="16">
-        <v>110.0</v>
+        <v>90.0</v>
       </c>
       <c r="G43" s="17">
         <f t="shared" si="2"/>
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H43" s="16">
-        <v>130.0</v>
+        <v>35.0</v>
       </c>
       <c r="I43" s="18">
-        <f t="shared" si="16"/>
-        <v>3.265384615</v>
+        <f t="shared" si="3"/>
+        <v>12.97142857</v>
       </c>
       <c r="J43" s="16">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="K43" s="16">
         <v>0.0</v>
@@ -6357,11 +6462,11 @@
         <v>21.0</v>
       </c>
       <c r="M43" s="16">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="N43" s="4">
         <f t="shared" si="4"/>
-        <v>0.2545454545</v>
+        <v>0.3555555556</v>
       </c>
       <c r="O43" s="4">
         <f t="shared" si="5"/>
@@ -6369,69 +6474,69 @@
       </c>
       <c r="P43" s="4">
         <f t="shared" si="6"/>
-        <v>0.7636363636</v>
+        <v>0.9333333333</v>
       </c>
       <c r="Q43" s="14">
         <f t="shared" si="7"/>
-        <v>0.05074878008</v>
+        <v>0.01850220264</v>
       </c>
       <c r="R43" s="19">
-        <f t="shared" ref="R43:S43" si="32">R32</f>
-        <v>0.795</v>
-      </c>
-      <c r="S43" s="19" t="str">
-        <f t="shared" si="32"/>
-        <v/>
+        <f>R37</f>
+        <v>0.648</v>
+      </c>
+      <c r="S43" s="19">
+        <f>S38</f>
+        <v>0.588</v>
       </c>
       <c r="T43" s="19">
-        <f t="shared" si="11"/>
-        <v>0.795</v>
+        <f t="shared" si="12"/>
+        <v>0.618</v>
       </c>
       <c r="U43" s="19">
         <f t="shared" si="9"/>
-        <v>3.987556667</v>
+        <v>11.87606349</v>
       </c>
       <c r="V43" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AJ43" s="24"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C44" s="14">
-        <v>1.92</v>
+        <v>1.46</v>
       </c>
       <c r="D44" s="15">
         <v>454.0</v>
       </c>
       <c r="E44" s="3">
         <f t="shared" si="1"/>
-        <v>1.92</v>
+        <v>1.46</v>
       </c>
       <c r="F44" s="16">
-        <v>110.0</v>
+        <v>120.0</v>
       </c>
       <c r="G44" s="17">
         <f t="shared" si="2"/>
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H44" s="16">
         <v>35.0</v>
       </c>
       <c r="I44" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="3"/>
         <v>12.97142857</v>
       </c>
       <c r="J44" s="16">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="K44" s="16">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="L44" s="16">
         <v>22.0</v>
@@ -6441,169 +6546,166 @@
       </c>
       <c r="N44" s="4">
         <f t="shared" si="4"/>
-        <v>0.3272727273</v>
+        <v>0.2333333333</v>
       </c>
       <c r="O44" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P44" s="4">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.7333333333</v>
       </c>
       <c r="Q44" s="14">
         <f t="shared" si="7"/>
-        <v>0.01644640235</v>
+        <v>0.01607929515</v>
       </c>
       <c r="R44" s="19">
-        <f t="shared" ref="R44:S44" si="33">R32</f>
-        <v>0.795</v>
-      </c>
-      <c r="S44" s="19" t="str">
-        <f t="shared" si="33"/>
-        <v/>
+        <f t="shared" ref="R44:S44" si="34">R39</f>
+        <v>0.74</v>
+      </c>
+      <c r="S44" s="19">
+        <f t="shared" si="34"/>
+        <v>0.83</v>
       </c>
       <c r="T44" s="19">
-        <f t="shared" si="11"/>
-        <v>0.795</v>
+        <f t="shared" si="12"/>
+        <v>0.785</v>
       </c>
       <c r="U44" s="19">
         <f t="shared" si="9"/>
-        <v>15.81998377</v>
+        <v>11.39146119</v>
       </c>
       <c r="V44" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AJ44" s="24"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C45" s="14">
-        <v>9.08</v>
-      </c>
-      <c r="D45" s="25">
-        <f>20*28.3*4</f>
-        <v>2264</v>
+        <v>1.5</v>
+      </c>
+      <c r="D45" s="15">
+        <v>454.0</v>
       </c>
       <c r="E45" s="3">
         <f t="shared" si="1"/>
-        <v>1.820812721</v>
+        <v>1.5</v>
       </c>
       <c r="F45" s="16">
-        <v>120.0</v>
+        <v>130.0</v>
       </c>
       <c r="G45" s="17">
         <f t="shared" si="2"/>
-        <v>104.5</v>
+        <v>119</v>
       </c>
       <c r="H45" s="16">
-        <v>35.0</v>
+        <v>91.0</v>
       </c>
       <c r="I45" s="18">
-        <f t="shared" si="16"/>
-        <v>64.68571429</v>
+        <f t="shared" si="3"/>
+        <v>4.989010989</v>
       </c>
       <c r="J45" s="16">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="K45" s="16">
-        <v>0.5</v>
+        <v>7.0</v>
       </c>
       <c r="L45" s="16">
-        <v>21.0</v>
+        <v>2.0</v>
       </c>
       <c r="M45" s="16">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="N45" s="4">
         <f t="shared" si="4"/>
-        <v>0.2666666667</v>
+        <v>0.4307692308</v>
       </c>
       <c r="O45" s="4">
         <f t="shared" si="5"/>
-        <v>0.0375</v>
+        <v>0.4846153846</v>
       </c>
       <c r="P45" s="4">
         <f t="shared" si="6"/>
-        <v>0.7</v>
+        <v>0.06153846154</v>
       </c>
       <c r="Q45" s="14">
         <f t="shared" si="7"/>
-        <v>0.01754637809</v>
+        <v>0.02147577093</v>
       </c>
       <c r="R45" s="19">
-        <f t="shared" ref="R45:S45" si="34">R32</f>
-        <v>0.795</v>
-      </c>
-      <c r="S45" s="19" t="str">
-        <f t="shared" si="34"/>
-        <v/>
+        <v>0.7</v>
+      </c>
+      <c r="S45" s="19">
+        <v>0.97</v>
       </c>
       <c r="T45" s="19">
-        <f t="shared" si="11"/>
-        <v>0.795</v>
+        <f t="shared" si="12"/>
+        <v>0.835</v>
       </c>
       <c r="U45" s="19">
         <f t="shared" si="9"/>
-        <v>12.08226558</v>
+        <v>16.74874951</v>
       </c>
       <c r="V45" s="20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AJ45" s="24"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C46" s="14">
-        <v>1.58</v>
-      </c>
-      <c r="D46" s="25">
-        <f>16*28.3</f>
-        <v>452.8</v>
+        <v>1.16</v>
+      </c>
+      <c r="D46" s="27">
+        <f>15*28.3</f>
+        <v>424.5</v>
       </c>
       <c r="E46" s="3">
         <f t="shared" si="1"/>
-        <v>1.584187279</v>
+        <v>1.240612485</v>
       </c>
       <c r="F46" s="16">
-        <v>180.0</v>
+        <v>110.0</v>
       </c>
       <c r="G46" s="17">
         <f t="shared" si="2"/>
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H46" s="16">
-        <v>52.0</v>
+        <v>130.0</v>
       </c>
       <c r="I46" s="18">
-        <f t="shared" si="16"/>
-        <v>8.707692308</v>
+        <f t="shared" si="3"/>
+        <v>3.265384615</v>
       </c>
       <c r="J46" s="16">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="K46" s="16">
         <v>0.0</v>
       </c>
       <c r="L46" s="16">
-        <v>31.0</v>
+        <v>21.0</v>
       </c>
       <c r="M46" s="16">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="N46" s="4">
         <f t="shared" si="4"/>
-        <v>0.2888888889</v>
+        <v>0.2545454545</v>
       </c>
       <c r="O46" s="4">
         <f t="shared" si="5"/>
@@ -6611,14 +6713,14 @@
       </c>
       <c r="P46" s="4">
         <f t="shared" si="6"/>
-        <v>0.6888888889</v>
+        <v>0.7636363636</v>
       </c>
       <c r="Q46" s="14">
         <f t="shared" si="7"/>
-        <v>0.01395759717</v>
+        <v>0.05074878008</v>
       </c>
       <c r="R46" s="19">
-        <f t="shared" ref="R46:S46" si="35">R32</f>
+        <f t="shared" ref="R46:S46" si="35">R35</f>
         <v>0.795</v>
       </c>
       <c r="S46" s="19" t="str">
@@ -6626,78 +6728,64 @@
         <v/>
       </c>
       <c r="T46" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.795</v>
       </c>
       <c r="U46" s="19">
         <f t="shared" si="9"/>
-        <v>16.45459916</v>
+        <v>3.987556667</v>
       </c>
       <c r="V46" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="W46" s="26"/>
-      <c r="X46" s="26"/>
-      <c r="Y46" s="26"/>
-      <c r="Z46" s="26"/>
-      <c r="AA46" s="26"/>
-      <c r="AB46" s="26"/>
-      <c r="AC46" s="26"/>
-      <c r="AD46" s="26"/>
-      <c r="AE46" s="26"/>
-      <c r="AF46" s="26"/>
-      <c r="AG46" s="26"/>
-      <c r="AH46" s="26"/>
-      <c r="AI46" s="26"/>
-      <c r="AJ46" s="27"/>
+        <v>139</v>
+      </c>
+      <c r="AJ46" s="24"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C47" s="14">
-        <v>0.64</v>
-      </c>
-      <c r="D47" s="25">
-        <f>15*28.3</f>
-        <v>424.5</v>
+        <v>1.92</v>
+      </c>
+      <c r="D47" s="15">
+        <v>454.0</v>
       </c>
       <c r="E47" s="3">
         <f t="shared" si="1"/>
-        <v>0.6844758539</v>
+        <v>1.92</v>
       </c>
       <c r="F47" s="16">
-        <v>70.0</v>
+        <v>110.0</v>
       </c>
       <c r="G47" s="17">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="H47" s="16">
-        <v>125.0</v>
+        <v>35.0</v>
       </c>
       <c r="I47" s="18">
-        <f t="shared" si="16"/>
-        <v>3.396</v>
+        <f t="shared" si="3"/>
+        <v>12.97142857</v>
       </c>
       <c r="J47" s="16">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="K47" s="16">
         <v>0.0</v>
       </c>
       <c r="L47" s="16">
-        <v>12.0</v>
+        <v>22.0</v>
       </c>
       <c r="M47" s="16">
         <v>4.0</v>
       </c>
       <c r="N47" s="4">
         <f t="shared" si="4"/>
-        <v>0.2285714286</v>
+        <v>0.3272727273</v>
       </c>
       <c r="O47" s="4">
         <f t="shared" si="5"/>
@@ -6705,171 +6793,161 @@
       </c>
       <c r="P47" s="4">
         <f t="shared" si="6"/>
-        <v>0.6857142857</v>
+        <v>0.8</v>
       </c>
       <c r="Q47" s="14">
         <f t="shared" si="7"/>
-        <v>0.04711425206</v>
+        <v>0.01644640235</v>
       </c>
       <c r="R47" s="19">
-        <f>AVERAGE(0.597,0.782)</f>
-        <v>0.6895</v>
-      </c>
-      <c r="S47" s="19">
-        <f>AVERAGE(0.579,0.647)</f>
-        <v>0.613</v>
+        <f t="shared" ref="R47:S47" si="36">R35</f>
+        <v>0.795</v>
+      </c>
+      <c r="S47" s="19" t="str">
+        <f t="shared" si="36"/>
+        <v/>
       </c>
       <c r="T47" s="19">
-        <f t="shared" si="11"/>
-        <v>0.65125</v>
+        <f t="shared" si="12"/>
+        <v>0.795</v>
       </c>
       <c r="U47" s="19">
         <f t="shared" si="9"/>
-        <v>3.159492857</v>
+        <v>15.81998377</v>
       </c>
       <c r="V47" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="W47" s="21"/>
-      <c r="X47" s="21"/>
-      <c r="Y47" s="21"/>
-      <c r="Z47" s="21"/>
-      <c r="AA47" s="21"/>
-      <c r="AB47" s="21"/>
-      <c r="AC47" s="21"/>
-      <c r="AD47" s="21"/>
-      <c r="AE47" s="21"/>
-      <c r="AF47" s="21"/>
-      <c r="AG47" s="21"/>
-      <c r="AH47" s="21"/>
-      <c r="AI47" s="21"/>
-      <c r="AJ47" s="22"/>
+        <v>140</v>
+      </c>
+      <c r="AJ47" s="24"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C48" s="14">
-        <v>0.64</v>
-      </c>
-      <c r="D48" s="25">
-        <f>14.5*28.3</f>
-        <v>410.35</v>
+        <v>9.08</v>
+      </c>
+      <c r="D48" s="27">
+        <f>20*28.3*4</f>
+        <v>2264</v>
       </c>
       <c r="E48" s="3">
         <f t="shared" si="1"/>
-        <v>0.7080784696</v>
+        <v>1.820812721</v>
       </c>
       <c r="F48" s="16">
-        <v>25.0</v>
+        <v>120.0</v>
       </c>
       <c r="G48" s="17">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>104.5</v>
       </c>
       <c r="H48" s="16">
-        <v>121.0</v>
+        <v>35.0</v>
       </c>
       <c r="I48" s="18">
-        <f t="shared" si="16"/>
-        <v>3.391322314</v>
+        <f t="shared" si="3"/>
+        <v>64.68571429</v>
       </c>
       <c r="J48" s="16">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="K48" s="16">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="L48" s="16">
-        <v>5.0</v>
+        <v>21.0</v>
       </c>
       <c r="M48" s="16">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="N48" s="4">
         <f t="shared" si="4"/>
-        <v>0.16</v>
+        <v>0.2666666667</v>
       </c>
       <c r="O48" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.0375</v>
       </c>
       <c r="P48" s="4">
         <f t="shared" si="6"/>
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="7"/>
-        <v>0.1887169489</v>
+        <v>0.01754637809</v>
       </c>
       <c r="R48" s="19">
-        <f>AVERAGE(0.73,0.89)</f>
-        <v>0.81</v>
-      </c>
-      <c r="S48" s="19"/>
+        <f t="shared" ref="R48:S48" si="37">R35</f>
+        <v>0.795</v>
+      </c>
+      <c r="S48" s="19" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
       <c r="T48" s="19">
-        <f t="shared" si="11"/>
-        <v>0.81</v>
+        <f t="shared" si="12"/>
+        <v>0.795</v>
       </c>
       <c r="U48" s="19">
         <f t="shared" si="9"/>
-        <v>0.6867427686</v>
+        <v>12.08226558</v>
       </c>
       <c r="V48" s="20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AJ48" s="24"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C49" s="14">
-        <v>1.32</v>
-      </c>
-      <c r="D49" s="25">
-        <f>13.5*28.3</f>
-        <v>382.05</v>
+        <v>1.58</v>
+      </c>
+      <c r="D49" s="27">
+        <f>16*28.3</f>
+        <v>452.8</v>
       </c>
       <c r="E49" s="3">
         <f t="shared" si="1"/>
-        <v>1.568590499</v>
+        <v>1.584187279</v>
       </c>
       <c r="F49" s="16">
-        <v>20.0</v>
+        <v>180.0</v>
       </c>
       <c r="G49" s="17">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="H49" s="16">
-        <v>121.0</v>
+        <v>52.0</v>
       </c>
       <c r="I49" s="18">
-        <f t="shared" si="16"/>
-        <v>3.157438017</v>
+        <f t="shared" si="3"/>
+        <v>8.707692308</v>
       </c>
       <c r="J49" s="16">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="K49" s="16">
         <v>0.0</v>
       </c>
       <c r="L49" s="16">
-        <v>3.0</v>
+        <v>31.0</v>
       </c>
       <c r="M49" s="16">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="N49" s="4">
         <f t="shared" si="4"/>
-        <v>0.4</v>
+        <v>0.2888888889</v>
       </c>
       <c r="O49" s="4">
         <f t="shared" si="5"/>
@@ -6877,64 +6955,77 @@
       </c>
       <c r="P49" s="4">
         <f t="shared" si="6"/>
-        <v>0.6</v>
+        <v>0.6888888889</v>
       </c>
       <c r="Q49" s="14">
         <f t="shared" si="7"/>
-        <v>0.2090302316</v>
+        <v>0.01395759717</v>
       </c>
       <c r="R49" s="19">
-        <f t="shared" ref="R49:S49" si="36">R48</f>
-        <v>0.81</v>
+        <f t="shared" ref="R49:S49" si="38">R35</f>
+        <v>0.795</v>
       </c>
       <c r="S49" s="19" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="T49" s="19">
-        <f t="shared" si="11"/>
-        <v>0.81</v>
+        <f t="shared" si="12"/>
+        <v>0.795</v>
       </c>
       <c r="U49" s="19">
         <f t="shared" si="9"/>
-        <v>1.550015026</v>
+        <v>16.45459916</v>
       </c>
       <c r="V49" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="AJ49" s="24"/>
+        <v>142</v>
+      </c>
+      <c r="W49" s="25"/>
+      <c r="X49" s="25"/>
+      <c r="Y49" s="25"/>
+      <c r="Z49" s="25"/>
+      <c r="AA49" s="25"/>
+      <c r="AB49" s="25"/>
+      <c r="AC49" s="25"/>
+      <c r="AD49" s="25"/>
+      <c r="AE49" s="25"/>
+      <c r="AF49" s="25"/>
+      <c r="AG49" s="25"/>
+      <c r="AH49" s="25"/>
+      <c r="AI49" s="25"/>
+      <c r="AJ49" s="26"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C50" s="14">
-        <v>0.98</v>
-      </c>
-      <c r="D50" s="25">
-        <f t="shared" ref="D50:D54" si="38">12*28.3</f>
-        <v>339.6</v>
+        <v>0.64</v>
+      </c>
+      <c r="D50" s="27">
+        <f>15*28.3</f>
+        <v>424.5</v>
       </c>
       <c r="E50" s="3">
         <f t="shared" si="1"/>
-        <v>1.310129564</v>
+        <v>0.6844758539</v>
       </c>
       <c r="F50" s="16">
         <v>70.0</v>
       </c>
       <c r="G50" s="17">
         <f t="shared" si="2"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H50" s="16">
-        <v>85.0</v>
+        <v>125.0</v>
       </c>
       <c r="I50" s="18">
-        <f t="shared" si="16"/>
-        <v>3.995294118</v>
+        <f t="shared" si="3"/>
+        <v>3.396</v>
       </c>
       <c r="J50" s="16">
         <v>4.0</v>
@@ -6946,7 +7037,7 @@
         <v>12.0</v>
       </c>
       <c r="M50" s="16">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="N50" s="4">
         <f t="shared" si="4"/>
@@ -6962,76 +7053,89 @@
       </c>
       <c r="Q50" s="14">
         <f t="shared" si="7"/>
-        <v>0.0613221437</v>
+        <v>0.04711425206</v>
       </c>
       <c r="R50" s="19">
-        <f t="shared" ref="R50:S50" si="37">R47</f>
+        <f>AVERAGE(0.597,0.782)</f>
         <v>0.6895</v>
       </c>
       <c r="S50" s="19">
-        <f t="shared" si="37"/>
+        <f>AVERAGE(0.579,0.647)</f>
         <v>0.613</v>
       </c>
       <c r="T50" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.65125</v>
       </c>
       <c r="U50" s="19">
         <f t="shared" si="9"/>
-        <v>2.427461499</v>
+        <v>3.159492857</v>
       </c>
       <c r="V50" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="AJ50" s="24"/>
+        <v>144</v>
+      </c>
+      <c r="W50" s="21"/>
+      <c r="X50" s="21"/>
+      <c r="Y50" s="21"/>
+      <c r="Z50" s="21"/>
+      <c r="AA50" s="21"/>
+      <c r="AB50" s="21"/>
+      <c r="AC50" s="21"/>
+      <c r="AD50" s="21"/>
+      <c r="AE50" s="21"/>
+      <c r="AF50" s="21"/>
+      <c r="AG50" s="21"/>
+      <c r="AH50" s="21"/>
+      <c r="AI50" s="21"/>
+      <c r="AJ50" s="22"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C51" s="14">
-        <v>1.97</v>
-      </c>
-      <c r="D51" s="25">
-        <f t="shared" si="38"/>
-        <v>339.6</v>
+        <v>0.64</v>
+      </c>
+      <c r="D51" s="27">
+        <f>14.5*28.3</f>
+        <v>410.35</v>
       </c>
       <c r="E51" s="3">
         <f t="shared" si="1"/>
-        <v>2.633627797</v>
+        <v>0.7080784696</v>
       </c>
       <c r="F51" s="16">
         <v>25.0</v>
       </c>
       <c r="G51" s="17">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H51" s="16">
-        <v>86.0</v>
+        <v>121.0</v>
       </c>
       <c r="I51" s="18">
-        <f t="shared" si="16"/>
-        <v>3.948837209</v>
+        <f t="shared" si="3"/>
+        <v>3.391322314</v>
       </c>
       <c r="J51" s="16">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K51" s="16">
         <v>0.0</v>
       </c>
       <c r="L51" s="16">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="M51" s="16">
         <v>2.0</v>
       </c>
       <c r="N51" s="4">
         <f t="shared" si="4"/>
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="O51" s="4">
         <f t="shared" si="5"/>
@@ -7039,226 +7143,223 @@
       </c>
       <c r="P51" s="4">
         <f t="shared" si="6"/>
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="Q51" s="14">
         <f t="shared" si="7"/>
-        <v>0.2494405183</v>
+        <v>0.1887169489</v>
       </c>
       <c r="R51" s="19">
-        <f t="shared" ref="R51:S51" si="39">R48</f>
+        <f>AVERAGE(0.73,0.89)</f>
         <v>0.81</v>
       </c>
-      <c r="S51" s="19" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
+      <c r="S51" s="19"/>
       <c r="T51" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.81</v>
       </c>
       <c r="U51" s="19">
         <f t="shared" si="9"/>
-        <v>1.039125487</v>
+        <v>0.6867427686</v>
       </c>
       <c r="V51" s="20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AJ51" s="24"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C52" s="14">
-        <v>1.16</v>
-      </c>
-      <c r="D52" s="25">
-        <f t="shared" si="38"/>
-        <v>339.6</v>
+        <v>1.32</v>
+      </c>
+      <c r="D52" s="27">
+        <f>13.5*28.3</f>
+        <v>382.05</v>
       </c>
       <c r="E52" s="3">
         <f t="shared" si="1"/>
-        <v>1.550765607</v>
+        <v>1.568590499</v>
       </c>
       <c r="F52" s="16">
-        <v>35.0</v>
+        <v>20.0</v>
       </c>
       <c r="G52" s="17">
         <f t="shared" si="2"/>
-        <v>20.5</v>
+        <v>12</v>
       </c>
       <c r="H52" s="16">
-        <v>81.0</v>
+        <v>121.0</v>
       </c>
       <c r="I52" s="18">
-        <f t="shared" si="16"/>
-        <v>4.192592593</v>
+        <f t="shared" si="3"/>
+        <v>3.157438017</v>
       </c>
       <c r="J52" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="K52" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="L52" s="16">
         <v>3.0</v>
       </c>
-      <c r="K52" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="L52" s="16">
-        <v>4.0</v>
-      </c>
       <c r="M52" s="16">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="N52" s="4">
         <f t="shared" si="4"/>
-        <v>0.3428571429</v>
+        <v>0.4</v>
       </c>
       <c r="O52" s="4">
         <f t="shared" si="5"/>
-        <v>0.1285714286</v>
+        <v>0</v>
       </c>
       <c r="P52" s="4">
         <f t="shared" si="6"/>
-        <v>0.4571428571</v>
+        <v>0.6</v>
       </c>
       <c r="Q52" s="14">
         <f t="shared" si="7"/>
-        <v>0.09222614841</v>
+        <v>0.2090302316</v>
       </c>
       <c r="R52" s="19">
-        <f t="shared" ref="R52:S52" si="40">R48</f>
+        <f t="shared" ref="R52:S52" si="39">R51</f>
         <v>0.81</v>
       </c>
       <c r="S52" s="19" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="T52" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.81</v>
       </c>
       <c r="U52" s="19">
         <f t="shared" si="9"/>
-        <v>3.011231527</v>
+        <v>1.550015026</v>
       </c>
       <c r="V52" s="20" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AJ52" s="24"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C53" s="14">
-        <v>1.92</v>
-      </c>
-      <c r="D53" s="25">
-        <f t="shared" si="38"/>
+        <v>0.98</v>
+      </c>
+      <c r="D53" s="27">
+        <f t="shared" ref="D53:D57" si="41">12*28.3</f>
         <v>339.6</v>
       </c>
       <c r="E53" s="3">
         <f t="shared" si="1"/>
-        <v>2.566784452</v>
+        <v>1.310129564</v>
       </c>
       <c r="F53" s="16">
-        <v>90.0</v>
+        <v>70.0</v>
       </c>
       <c r="G53" s="17">
         <f t="shared" si="2"/>
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="H53" s="16">
         <v>85.0</v>
       </c>
       <c r="I53" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="3"/>
         <v>3.995294118</v>
       </c>
       <c r="J53" s="16">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="K53" s="16">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="L53" s="16">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="M53" s="16">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="N53" s="4">
         <f t="shared" si="4"/>
-        <v>0.4444444444</v>
+        <v>0.2285714286</v>
       </c>
       <c r="O53" s="4">
         <f t="shared" si="5"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P53" s="4">
         <f t="shared" si="6"/>
-        <v>0.2666666667</v>
+        <v>0.6857142857</v>
       </c>
       <c r="Q53" s="14">
         <f t="shared" si="7"/>
-        <v>0.0480565371</v>
+        <v>0.0613221437</v>
       </c>
       <c r="R53" s="19">
-        <f t="shared" ref="R53:S53" si="41">R48</f>
-        <v>0.81</v>
-      </c>
-      <c r="S53" s="19" t="str">
-        <f t="shared" si="41"/>
-        <v/>
+        <f t="shared" ref="R53:S53" si="40">R50</f>
+        <v>0.6895</v>
+      </c>
+      <c r="S53" s="19">
+        <f t="shared" si="40"/>
+        <v>0.613</v>
       </c>
       <c r="T53" s="19">
-        <f t="shared" si="11"/>
-        <v>0.81</v>
+        <f t="shared" si="12"/>
+        <v>0.65125</v>
       </c>
       <c r="U53" s="19">
         <f t="shared" si="9"/>
-        <v>7.491176471</v>
+        <v>2.427461499</v>
       </c>
       <c r="V53" s="20" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AJ53" s="24"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C54" s="14">
-        <v>2.57</v>
-      </c>
-      <c r="D54" s="25">
-        <f t="shared" si="38"/>
+        <v>1.97</v>
+      </c>
+      <c r="D54" s="27">
+        <f t="shared" si="41"/>
         <v>339.6</v>
       </c>
       <c r="E54" s="3">
         <f t="shared" si="1"/>
-        <v>3.435747939</v>
+        <v>2.633627797</v>
       </c>
       <c r="F54" s="16">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="G54" s="17">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="H54" s="16">
-        <v>100.0</v>
+        <v>86.0</v>
       </c>
       <c r="I54" s="18">
-        <f t="shared" si="16"/>
-        <v>3.396</v>
+        <f t="shared" si="3"/>
+        <v>3.948837209</v>
       </c>
       <c r="J54" s="16">
         <v>2.0</v>
@@ -7267,14 +7368,14 @@
         <v>0.0</v>
       </c>
       <c r="L54" s="16">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="M54" s="16">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="N54" s="4">
         <f t="shared" si="4"/>
-        <v>0.2666666667</v>
+        <v>0.32</v>
       </c>
       <c r="O54" s="4">
         <f t="shared" si="5"/>
@@ -7282,14 +7383,14 @@
       </c>
       <c r="P54" s="4">
         <f t="shared" si="6"/>
-        <v>0.9333333333</v>
+        <v>0.96</v>
       </c>
       <c r="Q54" s="14">
         <f t="shared" si="7"/>
-        <v>0.3783863369</v>
+        <v>0.2494405183</v>
       </c>
       <c r="R54" s="19">
-        <f t="shared" ref="R54:S54" si="42">R48</f>
+        <f t="shared" ref="R54:S54" si="42">R51</f>
         <v>0.81</v>
       </c>
       <c r="S54" s="19" t="str">
@@ -7297,80 +7398,80 @@
         <v/>
       </c>
       <c r="T54" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.81</v>
       </c>
       <c r="U54" s="19">
         <f t="shared" si="9"/>
-        <v>0.5708451362</v>
+        <v>1.039125487</v>
       </c>
       <c r="V54" s="20" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AJ54" s="24"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C55" s="14">
-        <v>1.98</v>
-      </c>
-      <c r="D55" s="25">
-        <f>10*28.3</f>
-        <v>283</v>
+        <v>1.16</v>
+      </c>
+      <c r="D55" s="27">
+        <f t="shared" si="41"/>
+        <v>339.6</v>
       </c>
       <c r="E55" s="3">
         <f t="shared" si="1"/>
-        <v>3.17639576</v>
+        <v>1.550765607</v>
       </c>
       <c r="F55" s="16">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="G55" s="17">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>20.5</v>
       </c>
       <c r="H55" s="16">
-        <v>85.0</v>
+        <v>81.0</v>
       </c>
       <c r="I55" s="18">
-        <f t="shared" si="16"/>
-        <v>3.329411765</v>
+        <f t="shared" si="3"/>
+        <v>4.192592593</v>
       </c>
       <c r="J55" s="16">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="K55" s="16">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="L55" s="16">
+        <v>4.0</v>
+      </c>
+      <c r="M55" s="16">
         <v>3.0</v>
-      </c>
-      <c r="M55" s="16">
-        <v>2.0</v>
       </c>
       <c r="N55" s="4">
         <f t="shared" si="4"/>
-        <v>0.32</v>
+        <v>0.3428571429</v>
       </c>
       <c r="O55" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.1285714286</v>
       </c>
       <c r="P55" s="4">
         <f t="shared" si="6"/>
-        <v>0.48</v>
+        <v>0.4571428571</v>
       </c>
       <c r="Q55" s="14">
         <f t="shared" si="7"/>
-        <v>0.2973498233</v>
+        <v>0.09222614841</v>
       </c>
       <c r="R55" s="19">
-        <f t="shared" ref="R55:S55" si="43">R48</f>
+        <f t="shared" ref="R55:S55" si="43">R51</f>
         <v>0.81</v>
       </c>
       <c r="S55" s="19" t="str">
@@ -7378,144 +7479,146 @@
         <v/>
       </c>
       <c r="T55" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.81</v>
       </c>
       <c r="U55" s="19">
         <f t="shared" si="9"/>
-        <v>0.8717005348</v>
+        <v>3.011231527</v>
       </c>
       <c r="V55" s="20" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AJ55" s="24"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C56" s="14">
-        <v>6.44</v>
-      </c>
-      <c r="D56" s="25">
-        <f>10*454</f>
-        <v>4540</v>
+        <v>1.92</v>
+      </c>
+      <c r="D56" s="27">
+        <f t="shared" si="41"/>
+        <v>339.6</v>
       </c>
       <c r="E56" s="3">
         <f t="shared" si="1"/>
-        <v>0.644</v>
+        <v>2.566784452</v>
       </c>
       <c r="F56" s="16">
-        <v>110.0</v>
+        <v>90.0</v>
       </c>
       <c r="G56" s="17">
         <f t="shared" si="2"/>
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="H56" s="16">
-        <v>148.0</v>
+        <v>85.0</v>
       </c>
       <c r="I56" s="18">
-        <f t="shared" si="16"/>
-        <v>30.67567568</v>
+        <f t="shared" si="3"/>
+        <v>3.995294118</v>
       </c>
       <c r="J56" s="16">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="K56" s="16">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="L56" s="16">
-        <v>26.0</v>
+        <v>6.0</v>
       </c>
       <c r="M56" s="16">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="N56" s="4">
         <f t="shared" si="4"/>
-        <v>0.1090909091</v>
+        <v>0.4444444444</v>
       </c>
       <c r="O56" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="P56" s="4">
         <f t="shared" si="6"/>
-        <v>0.9454545455</v>
+        <v>0.2666666667</v>
       </c>
       <c r="Q56" s="14">
         <f t="shared" si="7"/>
-        <v>0.069979442</v>
+        <v>0.0480565371</v>
       </c>
       <c r="R56" s="19">
-        <v>0.99</v>
-      </c>
-      <c r="S56" s="19">
-        <v>1.0</v>
+        <f t="shared" ref="R56:S56" si="44">R51</f>
+        <v>0.81</v>
+      </c>
+      <c r="S56" s="19" t="str">
+        <f t="shared" si="44"/>
+        <v/>
       </c>
       <c r="T56" s="19">
-        <f t="shared" si="11"/>
-        <v>0.995</v>
+        <f t="shared" si="12"/>
+        <v>0.81</v>
       </c>
       <c r="U56" s="19">
         <f t="shared" si="9"/>
-        <v>1.551104888</v>
+        <v>7.491176471</v>
       </c>
       <c r="V56" s="20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AJ56" s="24"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C57" s="14">
-        <v>5.68</v>
-      </c>
-      <c r="D57" s="25">
-        <f t="shared" ref="D57:D58" si="45">5*454</f>
-        <v>2270</v>
+        <v>2.57</v>
+      </c>
+      <c r="D57" s="27">
+        <f t="shared" si="41"/>
+        <v>339.6</v>
       </c>
       <c r="E57" s="3">
         <f t="shared" si="1"/>
-        <v>1.136</v>
+        <v>3.435747939</v>
       </c>
       <c r="F57" s="16">
-        <v>110.0</v>
+        <v>30.0</v>
       </c>
       <c r="G57" s="17">
         <f t="shared" si="2"/>
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="H57" s="16">
-        <v>148.0</v>
+        <v>100.0</v>
       </c>
       <c r="I57" s="18">
-        <f t="shared" si="16"/>
-        <v>15.33783784</v>
+        <f t="shared" si="3"/>
+        <v>3.396</v>
       </c>
       <c r="J57" s="16">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="K57" s="16">
         <v>0.0</v>
       </c>
       <c r="L57" s="16">
-        <v>26.0</v>
+        <v>7.0</v>
       </c>
       <c r="M57" s="16">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="N57" s="4">
         <f t="shared" si="4"/>
-        <v>0.1090909091</v>
+        <v>0.2666666667</v>
       </c>
       <c r="O57" s="4">
         <f t="shared" si="5"/>
@@ -7523,80 +7626,80 @@
       </c>
       <c r="P57" s="4">
         <f t="shared" si="6"/>
-        <v>0.9454545455</v>
+        <v>0.9333333333</v>
       </c>
       <c r="Q57" s="14">
         <f t="shared" si="7"/>
-        <v>0.1234419971</v>
+        <v>0.3783863369</v>
       </c>
       <c r="R57" s="19">
-        <f t="shared" ref="R57:S57" si="44">R56</f>
-        <v>0.99</v>
-      </c>
-      <c r="S57" s="19">
-        <f t="shared" si="44"/>
-        <v>1</v>
+        <f t="shared" ref="R57:S57" si="45">R51</f>
+        <v>0.81</v>
+      </c>
+      <c r="S57" s="19" t="str">
+        <f t="shared" si="45"/>
+        <v/>
       </c>
       <c r="T57" s="19">
-        <f t="shared" si="11"/>
-        <v>0.995</v>
+        <f t="shared" si="12"/>
+        <v>0.81</v>
       </c>
       <c r="U57" s="19">
         <f t="shared" si="9"/>
-        <v>0.8793235457</v>
+        <v>0.5708451362</v>
       </c>
       <c r="V57" s="20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AJ57" s="24"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C58" s="14">
-        <v>5.34</v>
-      </c>
-      <c r="D58" s="25">
-        <f t="shared" si="45"/>
-        <v>2270</v>
+        <v>1.98</v>
+      </c>
+      <c r="D58" s="27">
+        <f>10*28.3</f>
+        <v>283</v>
       </c>
       <c r="E58" s="3">
         <f t="shared" si="1"/>
-        <v>1.068</v>
+        <v>3.17639576</v>
       </c>
       <c r="F58" s="16">
-        <v>110.0</v>
+        <v>25.0</v>
       </c>
       <c r="G58" s="17">
         <f t="shared" si="2"/>
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="H58" s="16">
-        <v>148.0</v>
+        <v>85.0</v>
       </c>
       <c r="I58" s="18">
-        <f t="shared" si="16"/>
-        <v>15.33783784</v>
+        <f t="shared" si="3"/>
+        <v>3.329411765</v>
       </c>
       <c r="J58" s="16">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="K58" s="16">
         <v>0.0</v>
       </c>
       <c r="L58" s="16">
-        <v>26.0</v>
+        <v>3.0</v>
       </c>
       <c r="M58" s="16">
         <v>2.0</v>
       </c>
       <c r="N58" s="4">
         <f t="shared" si="4"/>
-        <v>0.1090909091</v>
+        <v>0.32</v>
       </c>
       <c r="O58" s="4">
         <f t="shared" si="5"/>
@@ -7604,80 +7707,80 @@
       </c>
       <c r="P58" s="4">
         <f t="shared" si="6"/>
-        <v>0.9454545455</v>
+        <v>0.48</v>
       </c>
       <c r="Q58" s="14">
         <f t="shared" si="7"/>
-        <v>0.1160528634</v>
+        <v>0.2973498233</v>
       </c>
       <c r="R58" s="19">
-        <f t="shared" ref="R58:S58" si="46">R56</f>
-        <v>0.99</v>
-      </c>
-      <c r="S58" s="19">
+        <f t="shared" ref="R58:S58" si="46">R51</f>
+        <v>0.81</v>
+      </c>
+      <c r="S58" s="19" t="str">
         <f t="shared" si="46"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T58" s="19">
-        <f t="shared" si="11"/>
-        <v>0.995</v>
+        <f t="shared" si="12"/>
+        <v>0.81</v>
       </c>
       <c r="U58" s="19">
         <f t="shared" si="9"/>
-        <v>0.9353104381</v>
+        <v>0.8717005348</v>
       </c>
       <c r="V58" s="20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AJ58" s="24"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C59" s="14">
-        <v>3.78</v>
-      </c>
-      <c r="D59" s="25">
-        <f>3*454</f>
-        <v>1362</v>
+        <v>6.44</v>
+      </c>
+      <c r="D59" s="27">
+        <f>10*454</f>
+        <v>4540</v>
       </c>
       <c r="E59" s="3">
         <f t="shared" si="1"/>
-        <v>1.26</v>
+        <v>0.644</v>
       </c>
       <c r="F59" s="16">
-        <v>130.0</v>
+        <v>110.0</v>
       </c>
       <c r="G59" s="17">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="H59" s="16">
-        <v>130.0</v>
+        <v>148.0</v>
       </c>
       <c r="I59" s="18">
-        <f t="shared" si="16"/>
-        <v>10.47692308</v>
+        <f t="shared" si="3"/>
+        <v>30.67567568</v>
       </c>
       <c r="J59" s="16">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="K59" s="16">
         <v>0.0</v>
       </c>
       <c r="L59" s="16">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
       <c r="M59" s="16">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="N59" s="4">
         <f t="shared" si="4"/>
-        <v>0.06153846154</v>
+        <v>0.1090909091</v>
       </c>
       <c r="O59" s="4">
         <f t="shared" si="5"/>
@@ -7685,473 +7788,714 @@
       </c>
       <c r="P59" s="4">
         <f t="shared" si="6"/>
-        <v>1.015384615</v>
+        <v>0.9454545455</v>
       </c>
       <c r="Q59" s="14">
         <f t="shared" si="7"/>
-        <v>0.1803964758</v>
+        <v>0.069979442</v>
       </c>
       <c r="R59" s="19">
-        <f t="shared" ref="R59:S59" si="47">R56</f>
         <v>0.99</v>
       </c>
       <c r="S59" s="19">
-        <f t="shared" si="47"/>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="T59" s="19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.995</v>
       </c>
       <c r="U59" s="19">
         <f t="shared" si="9"/>
-        <v>0.3394233117</v>
+        <v>1.551104888</v>
       </c>
       <c r="V59" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="W59" s="26"/>
-      <c r="X59" s="26"/>
-      <c r="Y59" s="26"/>
-      <c r="Z59" s="26"/>
-      <c r="AA59" s="26"/>
-      <c r="AB59" s="26"/>
-      <c r="AC59" s="26"/>
-      <c r="AD59" s="26"/>
-      <c r="AE59" s="26"/>
-      <c r="AF59" s="26"/>
-      <c r="AG59" s="26"/>
-      <c r="AH59" s="26"/>
-      <c r="AI59" s="26"/>
-      <c r="AJ59" s="27"/>
+        <v>154</v>
+      </c>
+      <c r="AJ59" s="24"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C60" s="14">
-        <v>23.74</v>
-      </c>
-      <c r="D60" s="25">
-        <f>4*454</f>
-        <v>1816</v>
+        <v>5.68</v>
+      </c>
+      <c r="D60" s="27">
+        <f t="shared" ref="D60:D61" si="48">5*454</f>
+        <v>2270</v>
       </c>
       <c r="E60" s="3">
         <f t="shared" si="1"/>
-        <v>5.935</v>
+        <v>1.136</v>
       </c>
       <c r="F60" s="16">
-        <v>120.0</v>
+        <v>110.0</v>
       </c>
       <c r="G60" s="17">
         <f t="shared" si="2"/>
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="H60" s="16">
-        <v>30.0</v>
+        <v>148.0</v>
       </c>
       <c r="I60" s="18">
-        <f t="shared" si="16"/>
-        <v>60.53333333</v>
+        <f t="shared" si="3"/>
+        <v>15.33783784</v>
       </c>
       <c r="J60" s="16">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
       <c r="K60" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="L60" s="16">
+        <v>26.0</v>
+      </c>
+      <c r="M60" s="16">
         <v>2.0</v>
-      </c>
-      <c r="L60" s="16">
-        <v>3.0</v>
-      </c>
-      <c r="M60" s="16">
-        <v>0.0</v>
       </c>
       <c r="N60" s="4">
         <f t="shared" si="4"/>
-        <v>0.8</v>
+        <v>0.1090909091</v>
       </c>
       <c r="O60" s="4">
         <f t="shared" si="5"/>
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="P60" s="4">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0.9454545455</v>
       </c>
       <c r="Q60" s="14">
         <f t="shared" si="7"/>
-        <v>0.01634085903</v>
+        <v>0.1234419971</v>
       </c>
       <c r="R60" s="19">
-        <v>0.463</v>
+        <f t="shared" ref="R60:S60" si="47">R59</f>
+        <v>0.99</v>
       </c>
       <c r="S60" s="19">
-        <f>AVERAGE(0.4,0.48)</f>
-        <v>0.44</v>
+        <f t="shared" si="47"/>
+        <v>1</v>
       </c>
       <c r="T60" s="19">
-        <f t="shared" si="11"/>
-        <v>0.4515</v>
+        <f t="shared" si="12"/>
+        <v>0.995</v>
       </c>
       <c r="U60" s="19">
         <f t="shared" si="9"/>
-        <v>22.1041011</v>
+        <v>0.8793235457</v>
       </c>
       <c r="V60" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="W60" s="21"/>
-      <c r="X60" s="21"/>
-      <c r="Y60" s="21"/>
-      <c r="Z60" s="21"/>
-      <c r="AA60" s="21"/>
-      <c r="AB60" s="21"/>
-      <c r="AC60" s="21"/>
-      <c r="AD60" s="21"/>
-      <c r="AE60" s="21"/>
-      <c r="AF60" s="21"/>
-      <c r="AG60" s="21"/>
-      <c r="AH60" s="21"/>
-      <c r="AI60" s="21"/>
-      <c r="AJ60" s="22"/>
+        <v>155</v>
+      </c>
+      <c r="AJ60" s="24"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C61" s="14">
-        <v>6.22</v>
-      </c>
-      <c r="D61" s="25">
-        <f>32*28.3</f>
-        <v>905.6</v>
+        <v>5.34</v>
+      </c>
+      <c r="D61" s="27">
+        <f t="shared" si="48"/>
+        <v>2270</v>
       </c>
       <c r="E61" s="3">
         <f t="shared" si="1"/>
-        <v>3.118242049</v>
+        <v>1.068</v>
       </c>
       <c r="F61" s="16">
-        <v>170.0</v>
+        <v>110.0</v>
       </c>
       <c r="G61" s="17">
         <f t="shared" si="2"/>
-        <v>150.5</v>
+        <v>108</v>
       </c>
       <c r="H61" s="16">
-        <v>45.0</v>
+        <v>148.0</v>
       </c>
       <c r="I61" s="18">
-        <f t="shared" si="16"/>
-        <v>20.12444444</v>
+        <f t="shared" si="3"/>
+        <v>15.33783784</v>
       </c>
       <c r="J61" s="16">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="K61" s="16">
-        <v>2.5</v>
+        <v>0.0</v>
       </c>
       <c r="L61" s="16">
-        <v>29.0</v>
+        <v>26.0</v>
       </c>
       <c r="M61" s="16">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="N61" s="4">
         <f t="shared" si="4"/>
-        <v>0.1411764706</v>
+        <v>0.1090909091</v>
       </c>
       <c r="O61" s="4">
         <f t="shared" si="5"/>
-        <v>0.1323529412</v>
+        <v>0</v>
       </c>
       <c r="P61" s="4">
         <f t="shared" si="6"/>
-        <v>0.6823529412</v>
+        <v>0.9454545455</v>
       </c>
       <c r="Q61" s="14">
         <f t="shared" si="7"/>
-        <v>0.05151280919</v>
+        <v>0.1160528634</v>
       </c>
       <c r="R61" s="19">
-        <v>0.677</v>
-      </c>
-      <c r="S61" s="19"/>
+        <f t="shared" ref="R61:S61" si="49">R59</f>
+        <v>0.99</v>
+      </c>
+      <c r="S61" s="19">
+        <f t="shared" si="49"/>
+        <v>1</v>
+      </c>
       <c r="T61" s="19">
-        <f t="shared" si="11"/>
-        <v>0.677</v>
+        <f t="shared" si="12"/>
+        <v>0.995</v>
       </c>
       <c r="U61" s="19">
         <f t="shared" si="9"/>
-        <v>1.855392321</v>
-      </c>
-      <c r="V61" s="23" t="s">
-        <v>154</v>
+        <v>0.9353104381</v>
+      </c>
+      <c r="V61" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="AJ61" s="24"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C62" s="14">
-        <v>3.46</v>
-      </c>
-      <c r="D62" s="25">
-        <f>16*28.3</f>
-        <v>452.8</v>
+        <v>3.78</v>
+      </c>
+      <c r="D62" s="27">
+        <f>3*454</f>
+        <v>1362</v>
       </c>
       <c r="E62" s="3">
         <f t="shared" si="1"/>
-        <v>3.469169611</v>
+        <v>1.26</v>
       </c>
       <c r="F62" s="16">
-        <v>170.0</v>
+        <v>130.0</v>
       </c>
       <c r="G62" s="17">
         <f t="shared" si="2"/>
-        <v>150.5</v>
+        <v>124</v>
       </c>
       <c r="H62" s="16">
-        <v>45.0</v>
+        <v>130.0</v>
       </c>
       <c r="I62" s="18">
-        <f t="shared" si="16"/>
-        <v>10.06222222</v>
+        <f t="shared" si="3"/>
+        <v>10.47692308</v>
       </c>
       <c r="J62" s="16">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="K62" s="16">
-        <v>2.5</v>
+        <v>0.0</v>
       </c>
       <c r="L62" s="16">
-        <v>29.0</v>
+        <v>33.0</v>
       </c>
       <c r="M62" s="16">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="N62" s="4">
         <f t="shared" si="4"/>
-        <v>0.1411764706</v>
+        <v>0.06153846154</v>
       </c>
       <c r="O62" s="4">
         <f t="shared" si="5"/>
-        <v>0.1323529412</v>
+        <v>0</v>
       </c>
       <c r="P62" s="4">
         <f t="shared" si="6"/>
-        <v>0.6823529412</v>
+        <v>1.015384615</v>
       </c>
       <c r="Q62" s="14">
         <f t="shared" si="7"/>
-        <v>0.05731007067</v>
+        <v>0.1803964758</v>
       </c>
       <c r="R62" s="19">
-        <f t="shared" ref="R62:S62" si="48">R61</f>
-        <v>0.677</v>
-      </c>
-      <c r="S62" s="19" t="str">
-        <f t="shared" si="48"/>
-        <v/>
+        <f t="shared" ref="R62:S62" si="50">R59</f>
+        <v>0.99</v>
+      </c>
+      <c r="S62" s="19">
+        <f t="shared" si="50"/>
+        <v>1</v>
       </c>
       <c r="T62" s="19">
-        <f t="shared" si="11"/>
-        <v>0.677</v>
+        <f t="shared" si="12"/>
+        <v>0.995</v>
       </c>
       <c r="U62" s="19">
         <f t="shared" si="9"/>
-        <v>1.667708126</v>
+        <v>0.3394233117</v>
       </c>
       <c r="V62" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="AJ62" s="24"/>
+        <v>157</v>
+      </c>
+      <c r="W62" s="25"/>
+      <c r="X62" s="25"/>
+      <c r="Y62" s="25"/>
+      <c r="Z62" s="25"/>
+      <c r="AA62" s="25"/>
+      <c r="AB62" s="25"/>
+      <c r="AC62" s="25"/>
+      <c r="AD62" s="25"/>
+      <c r="AE62" s="25"/>
+      <c r="AF62" s="25"/>
+      <c r="AG62" s="25"/>
+      <c r="AH62" s="25"/>
+      <c r="AI62" s="25"/>
+      <c r="AJ62" s="26"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C63" s="14">
-        <v>3.34</v>
-      </c>
-      <c r="D63" s="25">
-        <f>5*454</f>
-        <v>2270</v>
+        <v>23.74</v>
+      </c>
+      <c r="D63" s="27">
+        <f>4*454</f>
+        <v>1816</v>
       </c>
       <c r="E63" s="3">
         <f t="shared" si="1"/>
-        <v>0.668</v>
+        <v>5.935</v>
       </c>
       <c r="F63" s="16">
-        <v>160.0</v>
+        <v>120.0</v>
       </c>
       <c r="G63" s="17">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="H63" s="16">
-        <v>45.0</v>
+        <v>30.0</v>
       </c>
       <c r="I63" s="18">
-        <f t="shared" si="16"/>
-        <v>50.44444444</v>
+        <f t="shared" si="3"/>
+        <v>60.53333333</v>
       </c>
       <c r="J63" s="16">
+        <v>24.0</v>
+      </c>
+      <c r="K63" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="L63" s="16">
         <v>3.0</v>
       </c>
-      <c r="K63" s="16">
+      <c r="M63" s="16">
         <v>0.0</v>
-      </c>
-      <c r="L63" s="16">
-        <v>36.0</v>
-      </c>
-      <c r="M63" s="16">
-        <v>1.0</v>
       </c>
       <c r="N63" s="4">
         <f t="shared" si="4"/>
-        <v>0.075</v>
+        <v>0.8</v>
       </c>
       <c r="O63" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="P63" s="4">
         <f t="shared" si="6"/>
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="Q63" s="14">
         <f t="shared" si="7"/>
-        <v>0.02207048458</v>
+        <v>0.01634085903</v>
       </c>
       <c r="R63" s="19">
-        <v>0.616</v>
+        <v>0.463</v>
       </c>
       <c r="S63" s="19">
-        <f>AVERAGE(0.595,0.47)</f>
-        <v>0.5325</v>
+        <f>AVERAGE(0.4,0.48)</f>
+        <v>0.44</v>
       </c>
       <c r="T63" s="19">
-        <f t="shared" si="11"/>
-        <v>0.57425</v>
+        <f t="shared" si="12"/>
+        <v>0.4515</v>
       </c>
       <c r="U63" s="19">
         <f t="shared" si="9"/>
-        <v>1.951418413</v>
+        <v>22.1041011</v>
       </c>
       <c r="V63" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="AJ63" s="24"/>
+        <v>159</v>
+      </c>
+      <c r="W63" s="21"/>
+      <c r="X63" s="21"/>
+      <c r="Y63" s="21"/>
+      <c r="Z63" s="21"/>
+      <c r="AA63" s="21"/>
+      <c r="AB63" s="21"/>
+      <c r="AC63" s="21"/>
+      <c r="AD63" s="21"/>
+      <c r="AE63" s="21"/>
+      <c r="AF63" s="21"/>
+      <c r="AG63" s="21"/>
+      <c r="AH63" s="21"/>
+      <c r="AI63" s="21"/>
+      <c r="AJ63" s="22"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C64" s="14">
-        <v>1.64</v>
-      </c>
-      <c r="D64" s="25">
+        <v>6.22</v>
+      </c>
+      <c r="D64" s="27">
         <f>32*28.3</f>
         <v>905.6</v>
       </c>
       <c r="E64" s="3">
         <f t="shared" si="1"/>
-        <v>0.8221731449</v>
+        <v>3.118242049</v>
       </c>
       <c r="F64" s="16">
-        <v>150.0</v>
+        <v>170.0</v>
       </c>
       <c r="G64" s="17">
         <f t="shared" si="2"/>
-        <v>149.5</v>
+        <v>150.5</v>
       </c>
       <c r="H64" s="16">
-        <v>42.0</v>
+        <v>45.0</v>
       </c>
       <c r="I64" s="18">
-        <f t="shared" si="16"/>
-        <v>21.56190476</v>
+        <f t="shared" si="3"/>
+        <v>20.12444444</v>
       </c>
       <c r="J64" s="16">
+        <v>6.0</v>
+      </c>
+      <c r="K64" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="L64" s="16">
+        <v>29.0</v>
+      </c>
+      <c r="M64" s="16">
         <v>3.0</v>
-      </c>
-      <c r="K64" s="16">
-        <v>1.5</v>
-      </c>
-      <c r="L64" s="16">
-        <v>32.0</v>
-      </c>
-      <c r="M64" s="16">
-        <v>1.0</v>
       </c>
       <c r="N64" s="4">
         <f t="shared" si="4"/>
-        <v>0.08</v>
+        <v>0.1411764706</v>
       </c>
       <c r="O64" s="4">
         <f t="shared" si="5"/>
-        <v>0.09</v>
+        <v>0.1323529412</v>
       </c>
       <c r="P64" s="4">
         <f t="shared" si="6"/>
-        <v>0.8533333333</v>
+        <v>0.6823529412</v>
       </c>
       <c r="Q64" s="14">
         <f t="shared" si="7"/>
-        <v>0.02535335689</v>
+        <v>0.05151280919</v>
       </c>
       <c r="R64" s="19">
-        <f t="shared" ref="R64:S64" si="49">R63</f>
-        <v>0.616</v>
-      </c>
-      <c r="S64" s="19">
-        <f t="shared" si="49"/>
-        <v>0.5325</v>
-      </c>
+        <v>0.677</v>
+      </c>
+      <c r="S64" s="19"/>
       <c r="T64" s="19">
-        <f t="shared" si="11"/>
-        <v>0.57425</v>
+        <f t="shared" si="12"/>
+        <v>0.677</v>
       </c>
       <c r="U64" s="19">
         <f t="shared" si="9"/>
+        <v>1.855392321</v>
+      </c>
+      <c r="V64" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="AJ64" s="24"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C65" s="14">
+        <v>3.46</v>
+      </c>
+      <c r="D65" s="27">
+        <f>16*28.3</f>
+        <v>452.8</v>
+      </c>
+      <c r="E65" s="3">
+        <f t="shared" si="1"/>
+        <v>3.469169611</v>
+      </c>
+      <c r="F65" s="16">
+        <v>170.0</v>
+      </c>
+      <c r="G65" s="17">
+        <f t="shared" si="2"/>
+        <v>150.5</v>
+      </c>
+      <c r="H65" s="16">
+        <v>45.0</v>
+      </c>
+      <c r="I65" s="18">
+        <f t="shared" si="3"/>
+        <v>10.06222222</v>
+      </c>
+      <c r="J65" s="16">
+        <v>6.0</v>
+      </c>
+      <c r="K65" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="L65" s="16">
+        <v>29.0</v>
+      </c>
+      <c r="M65" s="16">
+        <v>3.0</v>
+      </c>
+      <c r="N65" s="4">
+        <f t="shared" si="4"/>
+        <v>0.1411764706</v>
+      </c>
+      <c r="O65" s="4">
+        <f t="shared" si="5"/>
+        <v>0.1323529412</v>
+      </c>
+      <c r="P65" s="4">
+        <f t="shared" si="6"/>
+        <v>0.6823529412</v>
+      </c>
+      <c r="Q65" s="14">
+        <f t="shared" si="7"/>
+        <v>0.05731007067</v>
+      </c>
+      <c r="R65" s="19">
+        <f t="shared" ref="R65:S65" si="51">R64</f>
+        <v>0.677</v>
+      </c>
+      <c r="S65" s="19" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="T65" s="19">
+        <f t="shared" si="12"/>
+        <v>0.677</v>
+      </c>
+      <c r="U65" s="19">
+        <f t="shared" si="9"/>
+        <v>1.667708126</v>
+      </c>
+      <c r="V65" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="AJ65" s="24"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C66" s="14">
+        <v>3.34</v>
+      </c>
+      <c r="D66" s="27">
+        <f>5*454</f>
+        <v>2270</v>
+      </c>
+      <c r="E66" s="3">
+        <f t="shared" si="1"/>
+        <v>0.668</v>
+      </c>
+      <c r="F66" s="16">
+        <v>160.0</v>
+      </c>
+      <c r="G66" s="17">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+      <c r="H66" s="16">
+        <v>45.0</v>
+      </c>
+      <c r="I66" s="18">
+        <f t="shared" si="3"/>
+        <v>50.44444444</v>
+      </c>
+      <c r="J66" s="16">
+        <v>3.0</v>
+      </c>
+      <c r="K66" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="L66" s="16">
+        <v>36.0</v>
+      </c>
+      <c r="M66" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="N66" s="4">
+        <f t="shared" si="4"/>
+        <v>0.075</v>
+      </c>
+      <c r="O66" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P66" s="4">
+        <f t="shared" si="6"/>
+        <v>0.9</v>
+      </c>
+      <c r="Q66" s="14">
+        <f t="shared" si="7"/>
+        <v>0.02207048458</v>
+      </c>
+      <c r="R66" s="19">
+        <v>0.616</v>
+      </c>
+      <c r="S66" s="19">
+        <f>AVERAGE(0.595,0.47)</f>
+        <v>0.5325</v>
+      </c>
+      <c r="T66" s="19">
+        <f t="shared" si="12"/>
+        <v>0.57425</v>
+      </c>
+      <c r="U66" s="19">
+        <f t="shared" si="9"/>
+        <v>1.951418413</v>
+      </c>
+      <c r="V66" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="AJ66" s="24"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C67" s="14">
+        <v>1.64</v>
+      </c>
+      <c r="D67" s="27">
+        <f>32*28.3</f>
+        <v>905.6</v>
+      </c>
+      <c r="E67" s="3">
+        <f t="shared" si="1"/>
+        <v>0.8221731449</v>
+      </c>
+      <c r="F67" s="16">
+        <v>150.0</v>
+      </c>
+      <c r="G67" s="17">
+        <f t="shared" si="2"/>
+        <v>149.5</v>
+      </c>
+      <c r="H67" s="16">
+        <v>42.0</v>
+      </c>
+      <c r="I67" s="18">
+        <f t="shared" si="3"/>
+        <v>21.56190476</v>
+      </c>
+      <c r="J67" s="16">
+        <v>3.0</v>
+      </c>
+      <c r="K67" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="L67" s="16">
+        <v>32.0</v>
+      </c>
+      <c r="M67" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="N67" s="4">
+        <f t="shared" si="4"/>
+        <v>0.08</v>
+      </c>
+      <c r="O67" s="4">
+        <f t="shared" si="5"/>
+        <v>0.09</v>
+      </c>
+      <c r="P67" s="4">
+        <f t="shared" si="6"/>
+        <v>0.8533333333</v>
+      </c>
+      <c r="Q67" s="14">
+        <f t="shared" si="7"/>
+        <v>0.02535335689</v>
+      </c>
+      <c r="R67" s="19">
+        <f t="shared" ref="R67:S67" si="52">R66</f>
+        <v>0.616</v>
+      </c>
+      <c r="S67" s="19">
+        <f t="shared" si="52"/>
+        <v>0.5325</v>
+      </c>
+      <c r="T67" s="19">
+        <f t="shared" si="12"/>
+        <v>0.57425</v>
+      </c>
+      <c r="U67" s="19">
+        <f t="shared" si="9"/>
         <v>1.81198885</v>
       </c>
-      <c r="V64" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="W64" s="26"/>
-      <c r="X64" s="26"/>
-      <c r="Y64" s="26"/>
-      <c r="Z64" s="26"/>
-      <c r="AA64" s="26"/>
-      <c r="AB64" s="26"/>
-      <c r="AC64" s="26"/>
-      <c r="AD64" s="26"/>
-      <c r="AE64" s="26"/>
-      <c r="AF64" s="26"/>
-      <c r="AG64" s="26"/>
-      <c r="AH64" s="26"/>
-      <c r="AI64" s="26"/>
-      <c r="AJ64" s="27"/>
+      <c r="V67" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="W67" s="25"/>
+      <c r="X67" s="25"/>
+      <c r="Y67" s="25"/>
+      <c r="Z67" s="25"/>
+      <c r="AA67" s="25"/>
+      <c r="AB67" s="25"/>
+      <c r="AC67" s="25"/>
+      <c r="AD67" s="25"/>
+      <c r="AE67" s="25"/>
+      <c r="AF67" s="25"/>
+      <c r="AG67" s="25"/>
+      <c r="AH67" s="25"/>
+      <c r="AI67" s="25"/>
+      <c r="AJ67" s="26"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$V$64"/>
+  <autoFilter ref="$A$1:$V$67"/>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="V2"/>
     <hyperlink r:id="rId2" ref="V3"/>
@@ -8216,8 +8560,11 @@
     <hyperlink r:id="rId61" ref="V62"/>
     <hyperlink r:id="rId62" ref="V63"/>
     <hyperlink r:id="rId63" ref="V64"/>
+    <hyperlink r:id="rId64" ref="V65"/>
+    <hyperlink r:id="rId65" ref="V66"/>
+    <hyperlink r:id="rId66" ref="V67"/>
   </hyperlinks>
-  <drawing r:id="rId64"/>
+  <drawing r:id="rId67"/>
 </worksheet>
 </file>
 
@@ -8230,7 +8577,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
